--- a/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
+++ b/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupocomellicombr-my.sharepoint.com/personal/kaio_vieira_comber_com_br/Documents/01_Controladoria/02_Fechamento/2026/09_Setembro/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="620" documentId="13_ncr:1_{3A511E21-6657-4480-B238-A9FB2481249E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245B9796-14F4-4D5A-AE25-94425E8BA766}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A61FA8E-6B07-4341-BE53-E60B9D0E3AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" tabRatio="723" firstSheet="5" activeTab="10" xr2:uid="{920362AF-D7E1-454D-B021-C9F79DFF3D14}"/>
+    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" tabRatio="723" firstSheet="5" activeTab="12" xr2:uid="{920362AF-D7E1-454D-B021-C9F79DFF3D14}"/>
   </bookViews>
   <sheets>
     <sheet name="Principais Transações" sheetId="2" state="hidden" r:id="rId1"/>
@@ -24,7 +24,9 @@
     <sheet name="Cronograma Fechamento" sheetId="23" r:id="rId9"/>
     <sheet name="Planilha2" sheetId="27" state="hidden" r:id="rId10"/>
     <sheet name="Cards Fechamento" sheetId="25" r:id="rId11"/>
-    <sheet name="Texto E-mail" sheetId="26" state="hidden" r:id="rId12"/>
+    <sheet name="Planilha3" sheetId="28" r:id="rId12"/>
+    <sheet name="Fluxo no Tempo" sheetId="29" r:id="rId30"/>
+    <sheet name="Texto E-mail" sheetId="26" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CAMINHOES (2)'!$B$7:$G$7</definedName>
@@ -92,19 +94,19 @@
     <definedName name="Z_C85FEBD2_4F70_4E73_9DDF_3EF2B1B507C0_.wvu.PrintTitles" localSheetId="5" hidden="1">'Consolidado- Comber'!$7:$7</definedName>
     <definedName name="Z_C85FEBD2_4F70_4E73_9DDF_3EF2B1B507C0_.wvu.PrintTitles" localSheetId="6" hidden="1">HOLDING!$7:$7</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <customWorkbookViews>
+    <customWorkbookView name="Barros, Samuel {PI} - Modo de exibição pessoal" guid="{C85FEBD2-4F70-4E73-9DDF-3EF2B1B507C0}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1362" windowHeight="547" tabRatio="287" activeSheetId="3"/>
+    <customWorkbookView name="Hauer, Flavia {PI} - Modo de exibição pessoal" guid="{272DF0F8-FD24-44E3-94C1-386D78F5B3AD}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="799" activeSheetId="1"/>
+    <customWorkbookView name="Administrador - Modo de exibição pessoal" guid="{42C49DAE-241A-424C-BE16-164C8D1282F8}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1362" windowHeight="518" activeSheetId="1"/>
+    <customWorkbookView name="40125673 - Modo de exibição pessoal" guid="{82D28B06-7129-4B14-BECA-4E1EF6D30C2C}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1020" windowHeight="529" activeSheetId="1"/>
+    <customWorkbookView name="Ana.Paula - Modo de exibição pessoal" guid="{5AD48A4A-9E8D-47D6-BA73-A4462D3E98C0}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1020" windowHeight="530" activeSheetId="1"/>
     <customWorkbookView name="40205357 - Modo de exibição pessoal" guid="{4D056326-B166-40DC-9CDF-108A95914A41}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1276" windowHeight="773" tabRatio="346" activeSheetId="1"/>
-    <customWorkbookView name="Ana.Paula - Modo de exibição pessoal" guid="{5AD48A4A-9E8D-47D6-BA73-A4462D3E98C0}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1020" windowHeight="530" activeSheetId="1"/>
-    <customWorkbookView name="40125673 - Modo de exibição pessoal" guid="{82D28B06-7129-4B14-BECA-4E1EF6D30C2C}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1020" windowHeight="529" activeSheetId="1"/>
-    <customWorkbookView name="Administrador - Modo de exibição pessoal" guid="{42C49DAE-241A-424C-BE16-164C8D1282F8}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1362" windowHeight="518" activeSheetId="1"/>
-    <customWorkbookView name="Hauer, Flavia {PI} - Modo de exibição pessoal" guid="{272DF0F8-FD24-44E3-94C1-386D78F5B3AD}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1276" windowHeight="799" activeSheetId="1"/>
-    <customWorkbookView name="Barros, Samuel {PI} - Modo de exibição pessoal" guid="{C85FEBD2-4F70-4E73-9DDF-3EF2B1B507C0}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1362" windowHeight="547" tabRatio="287" activeSheetId="3"/>
   </customWorkbookViews>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId13"/>
-    <pivotCache cacheId="1" r:id="rId14"/>
-    <pivotCache cacheId="2" r:id="rId15"/>
+    <pivotCache cacheId="3" r:id="rId14"/>
+    <pivotCache cacheId="4" r:id="rId15"/>
+    <pivotCache cacheId="5" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -126,7 +128,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -148,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="240">
   <si>
     <t>PS</t>
   </si>
@@ -759,9 +761,6 @@
     <t>Apuração de tributos</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Folha de pagamento</t>
   </si>
   <si>
@@ -789,9 +788,6 @@
     <t>Controladoria – Grupo Comber</t>
   </si>
   <si>
-    <t>Dica: para o corpo do e-mail, selecione A1:M34 na aba 'Cards Fechamento', copie e cole como imagem. As datas acima se atualizam sozinhas quando o mês muda.</t>
-  </si>
-  <si>
     <t>CRONOGRAMA FECHAMENTO - SETEMBRO 2026</t>
   </si>
   <si>
@@ -804,36 +800,88 @@
     <t>Kaio · Erica</t>
   </si>
   <si>
-    <t xml:space="preserve">Validação Fiscal</t>
+    <t>Validação Fiscal</t>
   </si>
   <si>
-    <t xml:space="preserve">Correção Validação Fiscal</t>
+    <t>Correção Validação Fiscal</t>
   </si>
   <si>
-    <t xml:space="preserve">Áreas apontadas</t>
+    <t>Áreas apontadas</t>
   </si>
   <si>
-    <t xml:space="preserve">Áreas apontadas na validação</t>
+    <t>Validação fiscal</t>
   </si>
   <si>
-    <t xml:space="preserve">Validação fiscal</t>
+    <t>Correção da validação fiscal</t>
   </si>
   <si>
-    <t xml:space="preserve">Correção da validação fiscal</t>
+    <t>Dica: para o corpo do e-mail, selecione A1:Q31 na aba 'Cards Fechamento', copie e cole como imagem. As datas acima se atualizam sozinhas quando o mês muda.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dica: para o corpo do e-mail, selecione A1:Q31 na aba 'Cards Fechamento', copie e cole como imagem. As datas acima se atualizam sozinhas quando o mês muda.</t>
+    <t>Iniciar apuração de Tributos</t>
+  </si>
+  <si>
+    <t>Marcus - Leania</t>
+  </si>
+  <si>
+    <t>Marcus - Fabiana</t>
+  </si>
+  <si>
+    <t>Marcus - Simone</t>
+  </si>
+  <si>
+    <t>Kaio - Erica</t>
+  </si>
+  <si>
+    <t>Joyce - Mariana</t>
+  </si>
+  <si>
+    <t>Compras/Vendas/Estoque/Escrita</t>
+  </si>
+  <si>
+    <t>Início das apurações fiscais</t>
+  </si>
+  <si>
+    <t>Início da contabilidade</t>
+  </si>
+  <si>
+    <t>Dia das correções</t>
+  </si>
+  <si>
+    <t>Trava do sistema e validação fiscal</t>
+  </si>
+  <si>
+    <t>Entrega dos impostos apurados (menos PIS/COFINS que precisa da contabilidade finalizada)</t>
+  </si>
+  <si>
+    <t>5 dias uteis depois do inicio das apurações</t>
+  </si>
+  <si>
+    <t>Entrega da contabilidade</t>
+  </si>
+  <si>
+    <t>Danilo - Elizete</t>
+  </si>
+  <si>
+    <t>Patricia - Regiclessia</t>
+  </si>
+  <si>
+    <t>Patricia - Luciene</t>
+  </si>
+  <si>
+    <t>Kaio - Gabriely</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-416]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="h:mm"/>
+    <numFmt numFmtId="190" formatCode="dd/mmm"/>
   </numFmts>
-  <fonts count="69" x14ac:knownFonts="1">
+  <fonts count="116" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1288,8 +1336,320 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF152C4E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF152C4E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF255E8E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF4A90C4"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2F7D6E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF2F7D6E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF2F7D6E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF2F7D6E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF548235"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF548235"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF152C4E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF26374A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8496A8"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1434,8 +1794,134 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF152C4E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF152C4E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF152C4E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF255E8E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A90C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4DAD6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4DAD6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F7D6E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFEBE9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFDCC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFDCC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="90">
+  <borders count="126">
     <border>
       <left/>
       <right/>
@@ -2408,13 +2894,389 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF152C4E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF152C4E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF152C4E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF255E8E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF255E8E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF255E8E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2E75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2E75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2E75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF4A90C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF4A90C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF4A90C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F7D6E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F7D6E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F7D6E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF548235"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF548235"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF548235"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2901,7 +3763,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3028,6 +3889,215 @@
     <xf numFmtId="0" fontId="31" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="56" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="24" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="24" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="24" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="24" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="22" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="24" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3046,7 +4116,6 @@
     <xf numFmtId="0" fontId="43" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3059,16 +4128,16 @@
     <xf numFmtId="0" fontId="44" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3089,187 +4158,6 @@
     <xf numFmtId="0" fontId="44" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="24" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="24" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="22" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="24" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="19" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3282,35 +4170,165 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="56" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="30" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="31" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="78" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="33" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="34" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="35" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="36" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="24" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="37" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="38" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="39" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="40" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="41" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="42" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="43" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="44" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="45" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8251,7 +9269,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3927BF9-49EF-4835-B7DA-17D42CF52279}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3927BF9-49EF-4835-B7DA-17D42CF52279}" name="Tabela dinâmica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="B5:K18" firstHeaderRow="2" firstDataRow="2" firstDataCol="4"/>
   <pivotFields count="7">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -10167,7 +11185,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB242FCB-CC13-47BC-AB8D-6E570A68967E}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB242FCB-CC13-47BC-AB8D-6E570A68967E}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B3:F16" firstHeaderRow="1" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="14">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10431,7 +11449,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D33FD235-23B0-4A20-8B1C-BE92D82C9582}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D33FD235-23B0-4A20-8B1C-BE92D82C9582}" name="Tabela dinâmica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:A34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -11077,37 +12095,37 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{4D056326-B166-40DC-9CDF-108A95914A41}" state="hidden">
+    <customSheetView guid="{C85FEBD2-4F70-4E73-9DDF-3EF2B1B507C0}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{5AD48A4A-9E8D-47D6-BA73-A4462D3E98C0}" state="hidden">
+    <customSheetView guid="{272DF0F8-FD24-44E3-94C1-386D78F5B3AD}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId2"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{82D28B06-7129-4B14-BECA-4E1EF6D30C2C}" state="hidden">
+    <customSheetView guid="{42C49DAE-241A-424C-BE16-164C8D1282F8}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId3"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{42C49DAE-241A-424C-BE16-164C8D1282F8}" state="hidden">
+    <customSheetView guid="{82D28B06-7129-4B14-BECA-4E1EF6D30C2C}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId4"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{272DF0F8-FD24-44E3-94C1-386D78F5B3AD}" state="hidden">
+    <customSheetView guid="{5AD48A4A-9E8D-47D6-BA73-A4462D3E98C0}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId5"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{C85FEBD2-4F70-4E73-9DDF-3EF2B1B507C0}" state="hidden">
+    <customSheetView guid="{4D056326-B166-40DC-9CDF-108A95914A41}" state="hidden">
       <selection activeCell="B24" sqref="B24"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId6"/>
@@ -11153,573 +12171,646 @@
     <col min="17" max="17" width="1.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="290" t="s">
+    <row r="1" spans="2:16" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="190" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="196"/>
-      <c r="N2" s="196"/>
-      <c r="O2" s="196"/>
-      <c r="P2" s="196"/>
-    </row>
-    <row r="3" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="291" t="str">
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="191"/>
+      <c r="O2" s="191"/>
+      <c r="P2" s="191"/>
+    </row>
+    <row r="3" spans="2:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="192" t="str">
         <f>"GRUPO COMBER   ·   "&amp;_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- ")</f>
         <v>GRUPO COMBER   ·   SETEMBRO 2026</v>
       </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="196"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="196"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="292" t="s">
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
+      <c r="K3" s="191"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="191"/>
+    </row>
+    <row r="4" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="193" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="196"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
-      <c r="G4" s="196"/>
-      <c r="H4" s="196"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="196"/>
-      <c r="K4" s="196"/>
-      <c r="L4" s="196"/>
-      <c r="M4" s="196"/>
-      <c r="N4" s="196"/>
-      <c r="O4" s="196"/>
-      <c r="P4" s="196"/>
-    </row>
-    <row r="5" ht="2.4" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="293" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="294"/>
-      <c r="D6" s="295"/>
-      <c r="F6" s="297" t="str">
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="191"/>
+      <c r="L4" s="191"/>
+      <c r="M4" s="191"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="191"/>
+      <c r="P4" s="191"/>
+    </row>
+    <row r="5" spans="2:16" ht="2.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="196" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="197"/>
+      <c r="D6" s="198"/>
+      <c r="F6" s="230" t="str">
         <f>'Cronograma Fechamento'!$C$33&amp;"º DIA ÚTIL"</f>
         <v>1º DIA ÚTIL</v>
       </c>
-      <c r="G6" s="298"/>
-      <c r="H6" s="299"/>
-      <c r="J6" s="297" t="str">
+      <c r="G6" s="231"/>
+      <c r="H6" s="232"/>
+      <c r="J6" s="230" t="str">
         <f>'Cronograma Fechamento'!$C$34&amp;"º DIA ÚTIL"</f>
         <v>2º DIA ÚTIL</v>
       </c>
-      <c r="K6" s="298"/>
-      <c r="L6" s="299"/>
-      <c r="N6" s="278" t="str">
+      <c r="K6" s="231"/>
+      <c r="L6" s="232"/>
+      <c r="N6" s="262" t="str">
         <f>'Cronograma Fechamento'!$C$35&amp;"º DIA ÚTIL"</f>
         <v>3º DIA ÚTIL</v>
       </c>
-      <c r="O6" s="279"/>
-      <c r="P6" s="280"/>
-    </row>
-    <row r="7" ht="43.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="308">
+      <c r="O6" s="263"/>
+      <c r="P6" s="264"/>
+    </row>
+    <row r="7" spans="2:16" ht="43.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="199">
         <v>46295</v>
       </c>
-      <c r="C7" s="232"/>
-      <c r="D7" s="296"/>
-      <c r="F7" s="300" t="str">
+      <c r="C7" s="200"/>
+      <c r="D7" s="201"/>
+      <c r="F7" s="233" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$33,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>01/out</v>
       </c>
-      <c r="G7" s="232"/>
-      <c r="H7" s="301"/>
-      <c r="J7" s="300" t="str">
+      <c r="G7" s="200"/>
+      <c r="H7" s="234"/>
+      <c r="J7" s="233" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$34,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>02/out</v>
       </c>
-      <c r="K7" s="232"/>
-      <c r="L7" s="301"/>
-      <c r="N7" s="281" t="str">
+      <c r="K7" s="200"/>
+      <c r="L7" s="234"/>
+      <c r="N7" s="265" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$35,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>05/out</v>
       </c>
-      <c r="O7" s="232"/>
-      <c r="P7" s="282"/>
-    </row>
-    <row r="8" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="309" t="s">
+      <c r="O7" s="200"/>
+      <c r="P7" s="266"/>
+    </row>
+    <row r="8" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="202" t="s">
         <v>200</v>
       </c>
-      <c r="C8" s="246"/>
-      <c r="D8" s="286"/>
-      <c r="F8" s="311" t="s">
-        <v>222</v>
-      </c>
-      <c r="G8" s="246"/>
-      <c r="H8" s="272"/>
-      <c r="J8" s="311" t="s">
-        <v>223</v>
-      </c>
-      <c r="K8" s="246"/>
-      <c r="L8" s="272"/>
-      <c r="N8" s="310" t="s">
+      <c r="C8" s="203"/>
+      <c r="D8" s="204"/>
+      <c r="F8" s="235" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="203"/>
+      <c r="H8" s="236"/>
+      <c r="J8" s="235" t="s">
+        <v>220</v>
+      </c>
+      <c r="K8" s="203"/>
+      <c r="L8" s="236"/>
+      <c r="N8" s="267" t="s">
         <v>201</v>
       </c>
-      <c r="O8" s="246"/>
-      <c r="P8" s="284"/>
-    </row>
-    <row r="9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="212" t="str">
+      <c r="O8" s="203"/>
+      <c r="P8" s="268"/>
+    </row>
+    <row r="9" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="205" t="str">
         <f>'Cronograma Fechamento'!C8</f>
         <v>Compras</v>
       </c>
-      <c r="C9" s="213"/>
-      <c r="D9" s="214"/>
-      <c r="F9" s="217" t="str">
+      <c r="C9" s="206"/>
+      <c r="D9" s="207"/>
+      <c r="F9" s="237" t="str">
         <f>'Cronograma Fechamento'!C12</f>
         <v>Validação Fiscal</v>
       </c>
-      <c r="G9" s="213"/>
-      <c r="H9" s="218"/>
-      <c r="J9" s="217" t="str">
+      <c r="G9" s="206"/>
+      <c r="H9" s="238"/>
+      <c r="J9" s="237" t="str">
         <f>'Cronograma Fechamento'!C14</f>
-        <v>Correção Validação Fiscal</v>
-      </c>
-      <c r="K9" s="213"/>
-      <c r="L9" s="218"/>
-      <c r="N9" s="215" t="str">
+        <v>Iniciar apuração de Tributos</v>
+      </c>
+      <c r="K9" s="206"/>
+      <c r="L9" s="238"/>
+      <c r="N9" s="269" t="str">
         <f>'Cronograma Fechamento'!C16</f>
         <v>Contas a Pagar</v>
       </c>
-      <c r="O9" s="213"/>
-      <c r="P9" s="216"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="285" t="str">
+      <c r="O9" s="206"/>
+      <c r="P9" s="270"/>
+    </row>
+    <row r="10" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="208" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D8</f>
         <v>›  Marcus · Leânia</v>
       </c>
-      <c r="C10" s="246"/>
-      <c r="D10" s="286"/>
-      <c r="F10" s="271" t="str">
+      <c r="C10" s="203"/>
+      <c r="D10" s="204"/>
+      <c r="F10" s="239" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D12</f>
         <v>›  Joyce · Mariana</v>
       </c>
-      <c r="G10" s="246"/>
-      <c r="H10" s="272"/>
-      <c r="J10" s="271" t="str">
+      <c r="G10" s="203"/>
+      <c r="H10" s="236"/>
+      <c r="J10" s="239" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D14</f>
-        <v>›  Áreas apontadas na validação</v>
-      </c>
-      <c r="K10" s="246"/>
-      <c r="L10" s="272"/>
-      <c r="N10" s="283" t="str">
+        <v>›  Joyce · Mariana</v>
+      </c>
+      <c r="K10" s="203"/>
+      <c r="L10" s="236"/>
+      <c r="N10" s="271" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D16</f>
         <v>›  Patrícia · Regicléssia · Jamile</v>
       </c>
-      <c r="O10" s="246"/>
-      <c r="P10" s="284"/>
-    </row>
-    <row r="11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="212" t="str">
+      <c r="O10" s="203"/>
+      <c r="P10" s="268"/>
+    </row>
+    <row r="11" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="205" t="str">
         <f>'Cronograma Fechamento'!C9</f>
         <v>Vendas</v>
       </c>
-      <c r="C11" s="213"/>
-      <c r="D11" s="214"/>
-      <c r="F11" s="274"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="270"/>
-      <c r="J11" s="274"/>
-      <c r="K11" s="196"/>
-      <c r="L11" s="270"/>
-      <c r="N11" s="215" t="str">
+      <c r="C11" s="206"/>
+      <c r="D11" s="207"/>
+      <c r="F11" s="240"/>
+      <c r="G11" s="191"/>
+      <c r="H11" s="241"/>
+      <c r="J11" s="316"/>
+      <c r="K11" s="191"/>
+      <c r="L11" s="241"/>
+      <c r="N11" s="269" t="str">
         <f>'Cronograma Fechamento'!C17</f>
         <v>Contas a Receber</v>
       </c>
-      <c r="O11" s="213"/>
-      <c r="P11" s="216"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="285" t="str">
+      <c r="O11" s="206"/>
+      <c r="P11" s="270"/>
+    </row>
+    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="208" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D9</f>
         <v>›  Marcus · Fabiana</v>
       </c>
-      <c r="C12" s="315"/>
-      <c r="D12" s="316"/>
-      <c r="F12" s="273"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="270"/>
-      <c r="J12" s="273"/>
-      <c r="K12" s="196"/>
-      <c r="L12" s="270"/>
-      <c r="N12" s="283" t="str">
+      <c r="C12" s="209"/>
+      <c r="D12" s="210"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="191"/>
+      <c r="H12" s="241"/>
+      <c r="J12" s="242"/>
+      <c r="K12" s="191"/>
+      <c r="L12" s="241"/>
+      <c r="N12" s="271" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D17</f>
         <v>›  Patrícia · Luciene · Jamile</v>
       </c>
-      <c r="O12" s="246"/>
-      <c r="P12" s="284"/>
-    </row>
-    <row r="13" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="212" t="str">
+      <c r="O12" s="203"/>
+      <c r="P12" s="268"/>
+    </row>
+    <row r="13" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="205" t="str">
         <f>'Cronograma Fechamento'!C10</f>
         <v>Estoque</v>
       </c>
-      <c r="C13" s="213"/>
-      <c r="D13" s="214"/>
-      <c r="F13" s="274"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="270"/>
-      <c r="J13" s="274"/>
-      <c r="K13" s="196"/>
-      <c r="L13" s="270"/>
-      <c r="N13" s="215" t="str">
+      <c r="C13" s="206"/>
+      <c r="D13" s="207"/>
+      <c r="F13" s="240"/>
+      <c r="G13" s="191"/>
+      <c r="H13" s="241"/>
+      <c r="J13" s="240"/>
+      <c r="K13" s="191"/>
+      <c r="L13" s="241"/>
+      <c r="N13" s="269" t="str">
         <f>'Cronograma Fechamento'!C18</f>
         <v>Tesouraria</v>
       </c>
-      <c r="O13" s="213"/>
-      <c r="P13" s="216"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="285" t="str">
+      <c r="O13" s="206"/>
+      <c r="P13" s="270"/>
+    </row>
+    <row r="14" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="208" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D10</f>
         <v>›  Marcus · Simone</v>
       </c>
-      <c r="C14" s="315"/>
-      <c r="D14" s="316"/>
-      <c r="F14" s="273"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="270"/>
-      <c r="J14" s="273"/>
-      <c r="K14" s="196"/>
-      <c r="L14" s="270"/>
-      <c r="N14" s="283" t="str">
+      <c r="C14" s="209"/>
+      <c r="D14" s="210"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="191"/>
+      <c r="H14" s="241"/>
+      <c r="J14" s="242"/>
+      <c r="K14" s="191"/>
+      <c r="L14" s="241"/>
+      <c r="N14" s="271" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D18</f>
         <v>›  Patrícia · Regicléssia · Jamile</v>
       </c>
-      <c r="O14" s="246"/>
-      <c r="P14" s="284"/>
-    </row>
-    <row r="15" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="212" t="str">
+      <c r="O14" s="203"/>
+      <c r="P14" s="268"/>
+    </row>
+    <row r="15" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="205" t="str">
         <f>'Cronograma Fechamento'!C11</f>
         <v>Escrita Fiscal</v>
       </c>
-      <c r="C15" s="317"/>
-      <c r="D15" s="214"/>
-      <c r="F15" s="274"/>
-      <c r="G15" s="196"/>
-      <c r="H15" s="270"/>
-      <c r="J15" s="274"/>
-      <c r="K15" s="196"/>
-      <c r="L15" s="270"/>
-      <c r="N15" s="215" t="str">
+      <c r="C15" s="206"/>
+      <c r="D15" s="207"/>
+      <c r="F15" s="240"/>
+      <c r="G15" s="191"/>
+      <c r="H15" s="241"/>
+      <c r="J15" s="240"/>
+      <c r="K15" s="191"/>
+      <c r="L15" s="241"/>
+      <c r="N15" s="269" t="str">
         <f>'Cronograma Fechamento'!C19</f>
         <v>Patrimônio (movimentação)</v>
       </c>
-      <c r="O15" s="213"/>
-      <c r="P15" s="216"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="285" t="str">
+      <c r="O15" s="206"/>
+      <c r="P15" s="270"/>
+    </row>
+    <row r="16" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="208" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D11</f>
         <v>›  Kaio · Erica</v>
       </c>
-      <c r="C16" s="315"/>
-      <c r="D16" s="316"/>
-      <c r="F16" s="273"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="270"/>
-      <c r="J16" s="273"/>
-      <c r="K16" s="196"/>
-      <c r="L16" s="270"/>
-      <c r="N16" s="283" t="str">
+      <c r="C16" s="209"/>
+      <c r="D16" s="210"/>
+      <c r="F16" s="242"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="241"/>
+      <c r="J16" s="242"/>
+      <c r="K16" s="191"/>
+      <c r="L16" s="241"/>
+      <c r="N16" s="271" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D19</f>
         <v>›  Gabriely · Jamile</v>
       </c>
-      <c r="O16" s="246"/>
-      <c r="P16" s="284"/>
-    </row>
-    <row r="17" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="275" t="str">
+      <c r="O16" s="203"/>
+      <c r="P16" s="268"/>
+    </row>
+    <row r="17" spans="2:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="211" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$7,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="C17" s="276"/>
-      <c r="D17" s="277"/>
-      <c r="F17" s="254" t="str">
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+      <c r="F17" s="243" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$7,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="G17" s="255"/>
-      <c r="H17" s="256"/>
-      <c r="J17" s="254" t="str">
+      <c r="G17" s="244"/>
+      <c r="H17" s="245"/>
+      <c r="J17" s="243" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$13,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="K17" s="255"/>
-      <c r="L17" s="256"/>
-      <c r="N17" s="287" t="str">
+      <c r="K17" s="244"/>
+      <c r="L17" s="245"/>
+      <c r="N17" s="272" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$15,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="O17" s="288"/>
-      <c r="P17" s="289"/>
-    </row>
-    <row r="18" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="257" t="str">
+      <c r="O17" s="273"/>
+      <c r="P17" s="274"/>
+    </row>
+    <row r="18" spans="2:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="214" t="str">
         <f>'Cronograma Fechamento'!$C$36&amp;"º DIA ÚTIL"</f>
         <v>4º DIA ÚTIL</v>
       </c>
-      <c r="C19" s="258"/>
-      <c r="D19" s="259"/>
-      <c r="F19" s="297" t="str">
+      <c r="C19" s="215"/>
+      <c r="D19" s="216"/>
+      <c r="F19" s="230" t="str">
         <f>'Cronograma Fechamento'!$C$37&amp;"º DIA ÚTIL"</f>
         <v>7º DIA ÚTIL</v>
       </c>
-      <c r="G19" s="298"/>
-      <c r="H19" s="299"/>
-      <c r="J19" s="239" t="str">
+      <c r="G19" s="231"/>
+      <c r="H19" s="232"/>
+      <c r="J19" s="246" t="str">
         <f>'Cronograma Fechamento'!$C$38&amp;"º DIA ÚTIL"</f>
         <v>9º DIA ÚTIL</v>
       </c>
-      <c r="K19" s="240"/>
-      <c r="L19" s="241"/>
-      <c r="N19" s="228" t="str">
+      <c r="K19" s="247"/>
+      <c r="L19" s="248"/>
+      <c r="N19" s="275" t="str">
         <f>'Cronograma Fechamento'!$C$39&amp;"º DIA ÚTIL"</f>
         <v>15º DIA ÚTIL</v>
       </c>
-      <c r="O19" s="229"/>
-      <c r="P19" s="230"/>
-    </row>
-    <row r="20" ht="43.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="260" t="str">
+      <c r="O19" s="276"/>
+      <c r="P19" s="277"/>
+    </row>
+    <row r="20" spans="2:16" ht="43.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="217" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$36,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>06/out</v>
       </c>
-      <c r="C20" s="232"/>
-      <c r="D20" s="261"/>
-      <c r="F20" s="300" t="str">
+      <c r="C20" s="200"/>
+      <c r="D20" s="218"/>
+      <c r="F20" s="233" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$37,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>09/out</v>
       </c>
-      <c r="G20" s="232"/>
-      <c r="H20" s="301"/>
-      <c r="J20" s="242" t="str">
+      <c r="G20" s="200"/>
+      <c r="H20" s="234"/>
+      <c r="J20" s="249" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$38,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>14/out</v>
       </c>
-      <c r="K20" s="232"/>
-      <c r="L20" s="243"/>
-      <c r="N20" s="231" t="str">
+      <c r="K20" s="200"/>
+      <c r="L20" s="250"/>
+      <c r="N20" s="278" t="str">
         <f>TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;'Cronograma Fechamento'!$C$39,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")</f>
         <v>22/out</v>
       </c>
-      <c r="O20" s="232"/>
-      <c r="P20" s="233"/>
-    </row>
-    <row r="21" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="314" t="s">
+      <c r="O20" s="200"/>
+      <c r="P20" s="279"/>
+    </row>
+    <row r="21" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="219" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="203"/>
+      <c r="D21" s="220"/>
+      <c r="F21" s="235" t="s">
+        <v>202</v>
+      </c>
+      <c r="G21" s="203"/>
+      <c r="H21" s="236"/>
+      <c r="J21" s="251" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="D21" s="263"/>
-      <c r="F21" s="311" t="s">
-        <v>202</v>
-      </c>
-      <c r="G21" s="246"/>
-      <c r="H21" s="272"/>
-      <c r="J21" s="313" t="s">
+      <c r="K21" s="203"/>
+      <c r="L21" s="252"/>
+      <c r="N21" s="280" t="s">
         <v>205</v>
       </c>
-      <c r="K21" s="246"/>
-      <c r="L21" s="247"/>
-      <c r="N21" s="312" t="s">
-        <v>206</v>
-      </c>
-      <c r="O21" s="246"/>
-      <c r="P21" s="269"/>
-    </row>
-    <row r="22" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="264" t="str">
+      <c r="O21" s="203"/>
+      <c r="P21" s="281"/>
+    </row>
+    <row r="22" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="221" t="str">
         <f>'Cronograma Fechamento'!C21</f>
         <v>Folha de Pagamento</v>
       </c>
-      <c r="C22" s="213"/>
-      <c r="D22" s="265"/>
-      <c r="F22" s="217" t="str">
+      <c r="C22" s="206"/>
+      <c r="D22" s="222"/>
+      <c r="F22" s="237" t="str">
         <f>'Cronograma Fechamento'!C23</f>
         <v>Tributos</v>
       </c>
-      <c r="G22" s="213"/>
-      <c r="H22" s="218"/>
-      <c r="J22" s="266" t="str">
+      <c r="G22" s="206"/>
+      <c r="H22" s="238"/>
+      <c r="J22" s="253" t="str">
         <f>'Cronograma Fechamento'!C25</f>
         <v>Contábil / Integração</v>
       </c>
-      <c r="K22" s="213"/>
-      <c r="L22" s="267"/>
-      <c r="N22" s="251" t="str">
+      <c r="K22" s="206"/>
+      <c r="L22" s="254"/>
+      <c r="N22" s="282" t="str">
         <f>'Cronograma Fechamento'!C27</f>
         <v>Balancete Fechado</v>
       </c>
-      <c r="O22" s="213"/>
-      <c r="P22" s="252"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="262" t="str">
+      <c r="O22" s="206"/>
+      <c r="P22" s="283"/>
+    </row>
+    <row r="23" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="223" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D21</f>
         <v>›  Danilo · Elizete</v>
       </c>
-      <c r="C23" s="246"/>
-      <c r="D23" s="263"/>
-      <c r="F23" s="271" t="str">
+      <c r="C23" s="203"/>
+      <c r="D23" s="220"/>
+      <c r="F23" s="239" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D23</f>
         <v>›  Joyce · Mariana</v>
       </c>
-      <c r="G23" s="246"/>
-      <c r="H23" s="272"/>
-      <c r="J23" s="245" t="str">
+      <c r="G23" s="203"/>
+      <c r="H23" s="236"/>
+      <c r="J23" s="255" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D25</f>
         <v>›  Joyce · Equipe Contábil</v>
       </c>
-      <c r="K23" s="246"/>
-      <c r="L23" s="247"/>
-      <c r="N23" s="268" t="str">
+      <c r="K23" s="203"/>
+      <c r="L23" s="252"/>
+      <c r="N23" s="284" t="str">
         <f>"›  "&amp;'Cronograma Fechamento'!D27</f>
         <v>›  Joyce · Equipe Contábil</v>
       </c>
-      <c r="O23" s="246"/>
-      <c r="P23" s="269"/>
-    </row>
-    <row r="24" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="223"/>
-      <c r="C24" s="196"/>
-      <c r="D24" s="224"/>
-      <c r="F24" s="274"/>
-      <c r="G24" s="196"/>
-      <c r="H24" s="270"/>
-      <c r="J24" s="250"/>
-      <c r="K24" s="196"/>
-      <c r="L24" s="244"/>
-      <c r="N24" s="253"/>
-      <c r="O24" s="196"/>
-      <c r="P24" s="235"/>
-    </row>
-    <row r="25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="249"/>
-      <c r="C25" s="196"/>
-      <c r="D25" s="224"/>
-      <c r="F25" s="273"/>
-      <c r="G25" s="196"/>
-      <c r="H25" s="270"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="196"/>
-      <c r="L25" s="244"/>
-      <c r="N25" s="234"/>
-      <c r="O25" s="196"/>
-      <c r="P25" s="235"/>
-    </row>
-    <row r="26" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="223"/>
-      <c r="C26" s="196"/>
-      <c r="D26" s="224"/>
-      <c r="F26" s="274"/>
-      <c r="G26" s="196"/>
-      <c r="H26" s="270"/>
-      <c r="J26" s="250"/>
-      <c r="K26" s="196"/>
-      <c r="L26" s="244"/>
-      <c r="N26" s="253"/>
-      <c r="O26" s="196"/>
-      <c r="P26" s="235"/>
-    </row>
-    <row r="27" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="236" t="str">
+      <c r="O23" s="203"/>
+      <c r="P23" s="281"/>
+    </row>
+    <row r="24" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="224"/>
+      <c r="C24" s="191"/>
+      <c r="D24" s="225"/>
+      <c r="F24" s="240"/>
+      <c r="G24" s="191"/>
+      <c r="H24" s="241"/>
+      <c r="J24" s="256"/>
+      <c r="K24" s="191"/>
+      <c r="L24" s="257"/>
+      <c r="N24" s="285"/>
+      <c r="O24" s="191"/>
+      <c r="P24" s="286"/>
+    </row>
+    <row r="25" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="226"/>
+      <c r="C25" s="191"/>
+      <c r="D25" s="225"/>
+      <c r="F25" s="242"/>
+      <c r="G25" s="191"/>
+      <c r="H25" s="241"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="191"/>
+      <c r="L25" s="257"/>
+      <c r="N25" s="287"/>
+      <c r="O25" s="191"/>
+      <c r="P25" s="286"/>
+    </row>
+    <row r="26" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="224"/>
+      <c r="C26" s="191"/>
+      <c r="D26" s="225"/>
+      <c r="F26" s="240"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="241"/>
+      <c r="J26" s="256"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="257"/>
+      <c r="N26" s="285"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="286"/>
+    </row>
+    <row r="27" spans="2:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="227" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$20,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="C27" s="237"/>
-      <c r="D27" s="238"/>
-      <c r="F27" s="254" t="str">
+      <c r="C27" s="228"/>
+      <c r="D27" s="229"/>
+      <c r="F27" s="243" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$22,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="G27" s="255"/>
-      <c r="H27" s="256"/>
-      <c r="J27" s="225" t="str">
+      <c r="G27" s="244"/>
+      <c r="H27" s="245"/>
+      <c r="J27" s="259" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$24,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="K27" s="226"/>
-      <c r="L27" s="227"/>
-      <c r="N27" s="219" t="str">
+      <c r="K27" s="260"/>
+      <c r="L27" s="261"/>
+      <c r="N27" s="288" t="str">
         <f>"até "&amp;TEXT('Cronograma Fechamento'!$G$26,"hh:mm")</f>
         <v>até 18:00</v>
       </c>
-      <c r="O27" s="220"/>
-      <c r="P27" s="221"/>
-    </row>
-    <row r="28" ht="4.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="222" t="str">
+      <c r="O27" s="289"/>
+      <c r="P27" s="290"/>
+    </row>
+    <row r="28" spans="2:16" ht="4.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="194" t="str">
         <f>"Horário limite de entrega: "&amp;TEXT('Cronograma Fechamento'!$G$7,"hh:mm")&amp;"   ·   "&amp;_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- ")</f>
         <v>Horário limite de entrega: 18:00   ·   SETEMBRO 2026</v>
       </c>
-      <c r="C29" s="196"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="196"/>
-      <c r="G29" s="196"/>
-      <c r="H29" s="196"/>
-      <c r="I29" s="196"/>
-      <c r="J29" s="196"/>
-      <c r="K29" s="196"/>
-      <c r="L29" s="196"/>
-      <c r="M29" s="196"/>
-      <c r="N29" s="196"/>
-      <c r="O29" s="196"/>
-      <c r="P29" s="196"/>
-    </row>
-    <row r="30" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="211" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="196"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="196"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="196"/>
-      <c r="I30" s="196"/>
-      <c r="J30" s="196"/>
-      <c r="K30" s="196"/>
-      <c r="L30" s="196"/>
-      <c r="M30" s="196"/>
-      <c r="N30" s="196"/>
-      <c r="O30" s="196"/>
-      <c r="P30" s="196"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="191"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="191"/>
+      <c r="H29" s="191"/>
+      <c r="I29" s="191"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="191"/>
+      <c r="N29" s="191"/>
+      <c r="O29" s="191"/>
+      <c r="P29" s="191"/>
+    </row>
+    <row r="30" spans="2:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="195" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="191"/>
+      <c r="D30" s="191"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="191"/>
+      <c r="M30" s="191"/>
+      <c r="N30" s="191"/>
+      <c r="O30" s="191"/>
+      <c r="P30" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="B4:P4"/>
@@ -11736,86 +12827,185 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="N27:P27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup orientation="landscape" fitToHeight="0" r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02680B3B-FC3B-4892-84D7-385D969FA45C}">
+  <dimension ref="C3:S10"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="8.88671875" style="318"/>
+    <col min="3" max="3" width="12.109375" style="318" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="318" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="318"/>
+    <col min="6" max="6" width="21.33203125" style="319" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="319" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="319"/>
+    <col min="9" max="9" width="18.33203125" style="319" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="319" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.44140625" style="319" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="318"/>
+    <col min="15" max="15" width="17.5546875" style="318" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="318"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="O3" s="320" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C4" s="317">
+        <v>46295</v>
+      </c>
+      <c r="D4" s="317"/>
+      <c r="F4" s="317">
+        <f>C4+1</f>
+        <v>46296</v>
+      </c>
+      <c r="G4" s="317"/>
+      <c r="I4" s="317">
+        <f>F4+1</f>
+        <v>46297</v>
+      </c>
+      <c r="J4" s="317"/>
+      <c r="K4" s="322"/>
+      <c r="L4" s="317">
+        <f>I4+4</f>
+        <v>46301</v>
+      </c>
+      <c r="M4" s="317"/>
+      <c r="O4" s="317">
+        <f>I4+7</f>
+        <v>46304</v>
+      </c>
+      <c r="P4" s="317"/>
+      <c r="R4" s="317">
+        <f>I4+13</f>
+        <v>46310</v>
+      </c>
+      <c r="S4" s="317"/>
+    </row>
+    <row r="5" spans="3:19" ht="92.4" x14ac:dyDescent="0.25">
+      <c r="C5" s="320" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="320" t="s">
+        <v>223</v>
+      </c>
+      <c r="F5" s="321" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="321" t="s">
+        <v>227</v>
+      </c>
+      <c r="I5" s="321" t="s">
+        <v>229</v>
+      </c>
+      <c r="J5" s="321" t="s">
+        <v>227</v>
+      </c>
+      <c r="K5" s="321"/>
+      <c r="L5" s="321" t="s">
+        <v>203</v>
+      </c>
+      <c r="M5" s="321" t="s">
+        <v>236</v>
+      </c>
+      <c r="O5" s="321" t="s">
+        <v>233</v>
+      </c>
+      <c r="P5" s="321" t="s">
+        <v>227</v>
+      </c>
+      <c r="R5" s="320" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="3:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C6" s="320" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="320" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="321" t="s">
+        <v>231</v>
+      </c>
+      <c r="G6" s="321" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" s="321" t="s">
+        <v>230</v>
+      </c>
+      <c r="J6" s="321" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6" s="321"/>
+      <c r="P6" s="319"/>
+    </row>
+    <row r="7" spans="3:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C7" s="320" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="320" t="s">
+        <v>225</v>
+      </c>
+      <c r="I7" s="321" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="321" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="3:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C8" s="320" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="320" t="s">
+        <v>226</v>
+      </c>
+      <c r="I8" s="321" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="321" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="3:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="I9" s="321" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="321" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="I10" s="321" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="321" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="L4:M4"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC49CAC-ED14-428C-A16D-1869315F902B}">
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
@@ -11831,32 +13021,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="305" t="str">
+      <c r="B2" s="313" t="str">
         <f>"Assunto:  Cronograma de Fechamento – "&amp;PROPER(_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- "))&amp;"  |  Grupo Comber"</f>
         <v>Assunto:  Cronograma de Fechamento – Setembro 2026  |  Grupo Comber</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
     </row>
     <row r="3" spans="2:4" ht="7.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="306"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
+      <c r="B3" s="314"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
     </row>
     <row r="5" spans="2:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="157" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C5" s="157"/>
       <c r="D5" s="157"/>
     </row>
     <row r="6" spans="2:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="307" t="str">
+      <c r="B6" s="315" t="str">
         <f>"Segue o cronograma de fechamento referente a "&amp;PROPER(_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- "))&amp;". Pedimos atenção especial aos prazos, pois o cumprimento de cada etapa é pré-requisito para a seguinte."</f>
         <v>Segue o cronograma de fechamento referente a Setembro 2026. Pedimos atenção especial aos prazos, pois o cumprimento de cada etapa é pré-requisito para a seguinte.</v>
       </c>
-      <c r="C6" s="303"/>
-      <c r="D6" s="303"/>
+      <c r="C6" s="311"/>
+      <c r="D6" s="311"/>
     </row>
     <row r="7" spans="2:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="157"/>
@@ -11869,18 +13059,18 @@
       <c r="D8" s="157"/>
     </row>
     <row r="9" spans="2:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="307" t="s">
+      <c r="B9" s="315" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="311"/>
+      <c r="D9" s="311"/>
+    </row>
+    <row r="10" spans="2:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="315" t="s">
         <v>209</v>
       </c>
-      <c r="C9" s="303"/>
-      <c r="D9" s="303"/>
-    </row>
-    <row r="10" spans="2:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="307" t="s">
-        <v>210</v>
-      </c>
-      <c r="C10" s="303"/>
-      <c r="D10" s="303"/>
+      <c r="C10" s="311"/>
+      <c r="D10" s="311"/>
     </row>
     <row r="11" spans="2:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="157"/>
@@ -11889,24 +13079,24 @@
     </row>
     <row r="12" spans="2:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C12" s="157"/>
       <c r="D12" s="157"/>
     </row>
     <row r="13" spans="2:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="302" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="303"/>
-      <c r="D13" s="303"/>
+      <c r="B13" s="310" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="311"/>
+      <c r="D13" s="311"/>
     </row>
     <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="304" t="s">
-        <v>224</v>
-      </c>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
+      <c r="B15" s="312" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="191"/>
+      <c r="D15" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -11920,6 +13110,984 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:S34"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="19" width="8.2" customWidth="1"/>
+    <col min="20" max="20" width="2.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2" ht="34" customHeight="1">
+      <c r="B2" s="323" t="str">
+        <f>"FLUXO DO FECHAMENTO NO TEMPO   ·   "&amp;_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- ")</f>
+        <v>FLUXO DO FECHAMENTO NO TEMPO   ·   SETEMBRO 2026</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Linha do tempo por dia útil: cada barra mostra quando a atividade acontece; ◆ marca a entrega (até 18:00). Datas calculadas pelo calendário da aba ListBox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATIVIDADE</t>
+        </is>
+      </c>
+      <c r="C5" s="327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSÁVEL</t>
+        </is>
+      </c>
+      <c r="D5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Últ. dia</t>
+        </is>
+      </c>
+      <c r="E5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1º d.u.</t>
+        </is>
+      </c>
+      <c r="F5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2º d.u.</t>
+        </is>
+      </c>
+      <c r="G5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3º d.u.</t>
+        </is>
+      </c>
+      <c r="H5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4º d.u.</t>
+        </is>
+      </c>
+      <c r="I5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5º d.u.</t>
+        </is>
+      </c>
+      <c r="J5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6º d.u.</t>
+        </is>
+      </c>
+      <c r="K5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7º d.u.</t>
+        </is>
+      </c>
+      <c r="L5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8º d.u.</t>
+        </is>
+      </c>
+      <c r="M5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9º d.u.</t>
+        </is>
+      </c>
+      <c r="N5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10º d.u.</t>
+        </is>
+      </c>
+      <c r="O5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11º d.u.</t>
+        </is>
+      </c>
+      <c r="P5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12º d.u.</t>
+        </is>
+      </c>
+      <c r="Q5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13º d.u.</t>
+        </is>
+      </c>
+      <c r="R5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14º d.u.</t>
+        </is>
+      </c>
+      <c r="S5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15º d.u.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data</t>
+        </is>
+      </c>
+      <c r="C6" s="329"/>
+      <c r="D6" s="332">
+        <f>WORKDAY(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;1,ListBox!$H:$H,ListBox!$A:$A,0,0),-1)</f>
+        <v>46295</v>
+      </c>
+      <c r="E6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;1,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46296</v>
+      </c>
+      <c r="F6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;2,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46297</v>
+      </c>
+      <c r="G6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;3,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46300</v>
+      </c>
+      <c r="H6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;4,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46301</v>
+      </c>
+      <c r="I6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;5,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46302</v>
+      </c>
+      <c r="J6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;6,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46303</v>
+      </c>
+      <c r="K6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;7,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46304</v>
+      </c>
+      <c r="L6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;8,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46308</v>
+      </c>
+      <c r="M6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;9,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46309</v>
+      </c>
+      <c r="N6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;10,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46310</v>
+      </c>
+      <c r="O6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;11,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46311</v>
+      </c>
+      <c r="P6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;12,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46314</v>
+      </c>
+      <c r="Q6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;13,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46315</v>
+      </c>
+      <c r="R6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;14,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46316</v>
+      </c>
+      <c r="S6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;15,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dia da semana</t>
+        </is>
+      </c>
+      <c r="C7" s="331"/>
+      <c r="D7" s="333" t="str">
+        <f>LOWER(TEXT(D6,"ddd"))</f>
+        <v>qua</v>
+      </c>
+      <c r="E7" s="333" t="str">
+        <f>LOWER(TEXT(E6,"ddd"))</f>
+        <v>qui</v>
+      </c>
+      <c r="F7" s="333" t="str">
+        <f>LOWER(TEXT(F6,"ddd"))</f>
+        <v>sex</v>
+      </c>
+      <c r="G7" s="333" t="str">
+        <f>LOWER(TEXT(G6,"ddd"))</f>
+        <v>seg</v>
+      </c>
+      <c r="H7" s="333" t="str">
+        <f>LOWER(TEXT(H6,"ddd"))</f>
+        <v>ter</v>
+      </c>
+      <c r="I7" s="333" t="str">
+        <f>LOWER(TEXT(I6,"ddd"))</f>
+        <v>qua</v>
+      </c>
+      <c r="J7" s="333" t="str">
+        <f>LOWER(TEXT(J6,"ddd"))</f>
+        <v>qui</v>
+      </c>
+      <c r="K7" s="333" t="str">
+        <f>LOWER(TEXT(K6,"ddd"))</f>
+        <v>sex</v>
+      </c>
+      <c r="L7" s="333" t="str">
+        <f>LOWER(TEXT(L6,"ddd"))</f>
+        <v>ter</v>
+      </c>
+      <c r="M7" s="333" t="str">
+        <f>LOWER(TEXT(M6,"ddd"))</f>
+        <v>qua</v>
+      </c>
+      <c r="N7" s="333" t="str">
+        <f>LOWER(TEXT(N6,"ddd"))</f>
+        <v>qui</v>
+      </c>
+      <c r="O7" s="333" t="str">
+        <f>LOWER(TEXT(O6,"ddd"))</f>
+        <v>sex</v>
+      </c>
+      <c r="P7" s="333" t="str">
+        <f>LOWER(TEXT(P6,"ddd"))</f>
+        <v>seg</v>
+      </c>
+      <c r="Q7" s="333" t="str">
+        <f>LOWER(TEXT(Q6,"ddd"))</f>
+        <v>ter</v>
+      </c>
+      <c r="R7" s="333" t="str">
+        <f>LOWER(TEXT(R6,"ddd"))</f>
+        <v>qua</v>
+      </c>
+      <c r="S7" s="333" t="str">
+        <f>LOWER(TEXT(S6,"ddd"))</f>
+        <v>qui</v>
+      </c>
+    </row>
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 · Fechamento operacional</t>
+        </is>
+      </c>
+      <c r="C9" s="335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrega das áreas operacionais no último dia do mês</t>
+        </is>
+      </c>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="336"/>
+      <c r="K9" s="336"/>
+      <c r="L9" s="336"/>
+      <c r="M9" s="336"/>
+      <c r="N9" s="336"/>
+      <c r="O9" s="336"/>
+      <c r="P9" s="336"/>
+      <c r="Q9" s="336"/>
+      <c r="R9" s="336"/>
+      <c r="S9" s="336"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="C10" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcus · Leânia</t>
+        </is>
+      </c>
+      <c r="D10" s="339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
+      <c r="G10" s="340"/>
+      <c r="H10" s="340"/>
+      <c r="I10" s="340"/>
+      <c r="J10" s="340"/>
+      <c r="K10" s="340"/>
+      <c r="L10" s="340"/>
+      <c r="M10" s="340"/>
+      <c r="N10" s="340"/>
+      <c r="O10" s="340"/>
+      <c r="P10" s="340"/>
+      <c r="Q10" s="340"/>
+      <c r="R10" s="340"/>
+      <c r="S10" s="340"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vendas</t>
+        </is>
+      </c>
+      <c r="C11" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcus · Fabiana</t>
+        </is>
+      </c>
+      <c r="D11" s="339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
+      <c r="G11" s="340"/>
+      <c r="H11" s="340"/>
+      <c r="I11" s="340"/>
+      <c r="J11" s="340"/>
+      <c r="K11" s="340"/>
+      <c r="L11" s="340"/>
+      <c r="M11" s="340"/>
+      <c r="N11" s="340"/>
+      <c r="O11" s="340"/>
+      <c r="P11" s="340"/>
+      <c r="Q11" s="340"/>
+      <c r="R11" s="340"/>
+      <c r="S11" s="340"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estoque</t>
+        </is>
+      </c>
+      <c r="C12" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcus · Simone</t>
+        </is>
+      </c>
+      <c r="D12" s="339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+      <c r="G12" s="340"/>
+      <c r="H12" s="340"/>
+      <c r="I12" s="340"/>
+      <c r="J12" s="340"/>
+      <c r="K12" s="340"/>
+      <c r="L12" s="340"/>
+      <c r="M12" s="340"/>
+      <c r="N12" s="340"/>
+      <c r="O12" s="340"/>
+      <c r="P12" s="340"/>
+      <c r="Q12" s="340"/>
+      <c r="R12" s="340"/>
+      <c r="S12" s="340"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escrita Fiscal</t>
+        </is>
+      </c>
+      <c r="C13" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaio · Erica</t>
+        </is>
+      </c>
+      <c r="D13" s="339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
+      <c r="G13" s="340"/>
+      <c r="H13" s="340"/>
+      <c r="I13" s="340"/>
+      <c r="J13" s="340"/>
+      <c r="K13" s="340"/>
+      <c r="L13" s="340"/>
+      <c r="M13" s="340"/>
+      <c r="N13" s="340"/>
+      <c r="O13" s="340"/>
+      <c r="P13" s="340"/>
+      <c r="Q13" s="340"/>
+      <c r="R13" s="340"/>
+      <c r="S13" s="340"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 · Trava e validação fiscal</t>
+        </is>
+      </c>
+      <c r="C14" s="342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema travado; o fiscal valida e as áreas corrigem no mesmo dia</t>
+        </is>
+      </c>
+      <c r="D14" s="343"/>
+      <c r="E14" s="343"/>
+      <c r="F14" s="343"/>
+      <c r="G14" s="343"/>
+      <c r="H14" s="343"/>
+      <c r="I14" s="343"/>
+      <c r="J14" s="343"/>
+      <c r="K14" s="343"/>
+      <c r="L14" s="343"/>
+      <c r="M14" s="343"/>
+      <c r="N14" s="343"/>
+      <c r="O14" s="343"/>
+      <c r="P14" s="343"/>
+      <c r="Q14" s="343"/>
+      <c r="R14" s="343"/>
+      <c r="S14" s="343"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trava do sistema e validação fiscal</t>
+        </is>
+      </c>
+      <c r="C15" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joyce · Mariana</t>
+        </is>
+      </c>
+      <c r="D15" s="340"/>
+      <c r="E15" s="344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="F15" s="340"/>
+      <c r="G15" s="340"/>
+      <c r="H15" s="340"/>
+      <c r="I15" s="340"/>
+      <c r="J15" s="340"/>
+      <c r="K15" s="340"/>
+      <c r="L15" s="340"/>
+      <c r="M15" s="340"/>
+      <c r="N15" s="340"/>
+      <c r="O15" s="340"/>
+      <c r="P15" s="340"/>
+      <c r="Q15" s="340"/>
+      <c r="R15" s="340"/>
+      <c r="S15" s="340"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dia das correções</t>
+        </is>
+      </c>
+      <c r="C16" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras · Vendas · Estoque · Escrita</t>
+        </is>
+      </c>
+      <c r="D16" s="340"/>
+      <c r="E16" s="344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="F16" s="340"/>
+      <c r="G16" s="340"/>
+      <c r="H16" s="340"/>
+      <c r="I16" s="340"/>
+      <c r="J16" s="340"/>
+      <c r="K16" s="340"/>
+      <c r="L16" s="340"/>
+      <c r="M16" s="340"/>
+      <c r="N16" s="340"/>
+      <c r="O16" s="340"/>
+      <c r="P16" s="340"/>
+      <c r="Q16" s="340"/>
+      <c r="R16" s="340"/>
+      <c r="S16" s="340"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 · Financeiro e patrimônio</t>
+        </is>
+      </c>
+      <c r="C17" s="346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entregas no dia em que começam apurações e contabilidade</t>
+        </is>
+      </c>
+      <c r="D17" s="347"/>
+      <c r="E17" s="347"/>
+      <c r="F17" s="347"/>
+      <c r="G17" s="347"/>
+      <c r="H17" s="347"/>
+      <c r="I17" s="347"/>
+      <c r="J17" s="347"/>
+      <c r="K17" s="347"/>
+      <c r="L17" s="347"/>
+      <c r="M17" s="347"/>
+      <c r="N17" s="347"/>
+      <c r="O17" s="347"/>
+      <c r="P17" s="347"/>
+      <c r="Q17" s="347"/>
+      <c r="R17" s="347"/>
+      <c r="S17" s="347"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contas a Pagar</t>
+        </is>
+      </c>
+      <c r="C18" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrícia · Regicléssia</t>
+        </is>
+      </c>
+      <c r="D18" s="340"/>
+      <c r="E18" s="340"/>
+      <c r="F18" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="G18" s="340"/>
+      <c r="H18" s="340"/>
+      <c r="I18" s="340"/>
+      <c r="J18" s="340"/>
+      <c r="K18" s="340"/>
+      <c r="L18" s="340"/>
+      <c r="M18" s="340"/>
+      <c r="N18" s="340"/>
+      <c r="O18" s="340"/>
+      <c r="P18" s="340"/>
+      <c r="Q18" s="340"/>
+      <c r="R18" s="340"/>
+      <c r="S18" s="340"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contas a Receber</t>
+        </is>
+      </c>
+      <c r="C19" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrícia · Luciene</t>
+        </is>
+      </c>
+      <c r="D19" s="340"/>
+      <c r="E19" s="340"/>
+      <c r="F19" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="G19" s="340"/>
+      <c r="H19" s="340"/>
+      <c r="I19" s="340"/>
+      <c r="J19" s="340"/>
+      <c r="K19" s="340"/>
+      <c r="L19" s="340"/>
+      <c r="M19" s="340"/>
+      <c r="N19" s="340"/>
+      <c r="O19" s="340"/>
+      <c r="P19" s="340"/>
+      <c r="Q19" s="340"/>
+      <c r="R19" s="340"/>
+      <c r="S19" s="340"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesouraria</t>
+        </is>
+      </c>
+      <c r="C20" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrícia · Regicléssia</t>
+        </is>
+      </c>
+      <c r="D20" s="340"/>
+      <c r="E20" s="340"/>
+      <c r="F20" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="G20" s="340"/>
+      <c r="H20" s="340"/>
+      <c r="I20" s="340"/>
+      <c r="J20" s="340"/>
+      <c r="K20" s="340"/>
+      <c r="L20" s="340"/>
+      <c r="M20" s="340"/>
+      <c r="N20" s="340"/>
+      <c r="O20" s="340"/>
+      <c r="P20" s="340"/>
+      <c r="Q20" s="340"/>
+      <c r="R20" s="340"/>
+      <c r="S20" s="340"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrimônio</t>
+        </is>
+      </c>
+      <c r="C21" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaio · Gabriely</t>
+        </is>
+      </c>
+      <c r="D21" s="340"/>
+      <c r="E21" s="340"/>
+      <c r="F21" s="348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="G21" s="340"/>
+      <c r="H21" s="340"/>
+      <c r="I21" s="340"/>
+      <c r="J21" s="340"/>
+      <c r="K21" s="340"/>
+      <c r="L21" s="340"/>
+      <c r="M21" s="340"/>
+      <c r="N21" s="340"/>
+      <c r="O21" s="340"/>
+      <c r="P21" s="340"/>
+      <c r="Q21" s="340"/>
+      <c r="R21" s="340"/>
+      <c r="S21" s="340"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 · Folha de pagamento</t>
+        </is>
+      </c>
+      <c r="C22" s="350"/>
+      <c r="D22" s="351"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
+      <c r="G22" s="351"/>
+      <c r="H22" s="351"/>
+      <c r="I22" s="351"/>
+      <c r="J22" s="351"/>
+      <c r="K22" s="351"/>
+      <c r="L22" s="351"/>
+      <c r="M22" s="351"/>
+      <c r="N22" s="351"/>
+      <c r="O22" s="351"/>
+      <c r="P22" s="351"/>
+      <c r="Q22" s="351"/>
+      <c r="R22" s="351"/>
+      <c r="S22" s="351"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Folha de pagamento</t>
+        </is>
+      </c>
+      <c r="C23" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Danilo · Elizete</t>
+        </is>
+      </c>
+      <c r="D23" s="340"/>
+      <c r="E23" s="340"/>
+      <c r="F23" s="340"/>
+      <c r="G23" s="340"/>
+      <c r="H23" s="352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="I23" s="340"/>
+      <c r="J23" s="340"/>
+      <c r="K23" s="340"/>
+      <c r="L23" s="340"/>
+      <c r="M23" s="340"/>
+      <c r="N23" s="340"/>
+      <c r="O23" s="340"/>
+      <c r="P23" s="340"/>
+      <c r="Q23" s="340"/>
+      <c r="R23" s="340"/>
+      <c r="S23" s="340"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 · Apurações fiscais</t>
+        </is>
+      </c>
+      <c r="C24" s="354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entrega 5 dias úteis após o início das apurações</t>
+        </is>
+      </c>
+      <c r="D24" s="355"/>
+      <c r="E24" s="355"/>
+      <c r="F24" s="355"/>
+      <c r="G24" s="355"/>
+      <c r="H24" s="355"/>
+      <c r="I24" s="355"/>
+      <c r="J24" s="355"/>
+      <c r="K24" s="355"/>
+      <c r="L24" s="355"/>
+      <c r="M24" s="355"/>
+      <c r="N24" s="355"/>
+      <c r="O24" s="355"/>
+      <c r="P24" s="355"/>
+      <c r="Q24" s="355"/>
+      <c r="R24" s="355"/>
+      <c r="S24" s="355"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apuração dos impostos (exceto PIS/COFINS)</t>
+        </is>
+      </c>
+      <c r="C25" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joyce · Mariana</t>
+        </is>
+      </c>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">início</t>
+        </is>
+      </c>
+      <c r="G25" s="357"/>
+      <c r="H25" s="357"/>
+      <c r="I25" s="357"/>
+      <c r="J25" s="357"/>
+      <c r="K25" s="358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="L25" s="340"/>
+      <c r="M25" s="340"/>
+      <c r="N25" s="340"/>
+      <c r="O25" s="340"/>
+      <c r="P25" s="340"/>
+      <c r="Q25" s="340"/>
+      <c r="R25" s="340"/>
+      <c r="S25" s="340"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apuração de PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="C26" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joyce · Mariana</t>
+        </is>
+      </c>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
+      <c r="G26" s="340"/>
+      <c r="H26" s="340"/>
+      <c r="I26" s="340"/>
+      <c r="J26" s="340"/>
+      <c r="K26" s="340"/>
+      <c r="L26" s="340"/>
+      <c r="M26" s="340"/>
+      <c r="N26" s="359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">após ▸</t>
+        </is>
+      </c>
+      <c r="O26" s="360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">···</t>
+        </is>
+      </c>
+      <c r="P26" s="360"/>
+      <c r="Q26" s="360"/>
+      <c r="R26" s="360"/>
+      <c r="S26" s="360"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 · Contabilidade</t>
+        </is>
+      </c>
+      <c r="C27" s="362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Começa com as apurações; libera o PIS/COFINS ao ser entregue</t>
+        </is>
+      </c>
+      <c r="D27" s="363"/>
+      <c r="E27" s="363"/>
+      <c r="F27" s="363"/>
+      <c r="G27" s="363"/>
+      <c r="H27" s="363"/>
+      <c r="I27" s="363"/>
+      <c r="J27" s="363"/>
+      <c r="K27" s="363"/>
+      <c r="L27" s="363"/>
+      <c r="M27" s="363"/>
+      <c r="N27" s="363"/>
+      <c r="O27" s="363"/>
+      <c r="P27" s="363"/>
+      <c r="Q27" s="363"/>
+      <c r="R27" s="363"/>
+      <c r="S27" s="363"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidade</t>
+        </is>
+      </c>
+      <c r="C28" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joyce · Equipe Contábil</t>
+        </is>
+      </c>
+      <c r="D28" s="340"/>
+      <c r="E28" s="340"/>
+      <c r="F28" s="364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">início</t>
+        </is>
+      </c>
+      <c r="G28" s="365"/>
+      <c r="H28" s="365"/>
+      <c r="I28" s="365"/>
+      <c r="J28" s="365"/>
+      <c r="K28" s="365"/>
+      <c r="L28" s="365"/>
+      <c r="M28" s="365"/>
+      <c r="N28" s="366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+      <c r="O28" s="340"/>
+      <c r="P28" s="340"/>
+      <c r="Q28" s="340"/>
+      <c r="R28" s="340"/>
+      <c r="S28" s="340"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balancete fechado</t>
+        </is>
+      </c>
+      <c r="C29" s="338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joyce · Equipe Contábil</t>
+        </is>
+      </c>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
+      <c r="G29" s="340"/>
+      <c r="H29" s="340"/>
+      <c r="I29" s="340"/>
+      <c r="J29" s="340"/>
+      <c r="K29" s="340"/>
+      <c r="L29" s="340"/>
+      <c r="M29" s="340"/>
+      <c r="N29" s="340"/>
+      <c r="O29" s="340"/>
+      <c r="P29" s="340"/>
+      <c r="Q29" s="340"/>
+      <c r="R29" s="340"/>
+      <c r="S29" s="366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEGENDA</t>
+        </is>
+      </c>
+      <c r="C31" s="368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆  entrega / prazo final (até 18:00)     ■  período de execução     ···  depende de etapa anterior (sem prazo fixo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → apurações, contabilidade e financeiro (2º d.u.) → folha (4º d.u.) → impostos (7º d.u.) → contabilidade (10º d.u.) → PIS/COFINS → balancete fechado (15º d.u.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (2º d.u. + 5 = 7º d.u.). PIS/COFINS só é apurado depois da contabilidade finalizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feriados e fins de semana não entram na contagem: as colunas mostram apenas dias úteis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="B3:S3"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="C14:S14"/>
+    <mergeCell ref="C17:S17"/>
+    <mergeCell ref="C22:S22"/>
+    <mergeCell ref="C24:S24"/>
+    <mergeCell ref="C27:S27"/>
+    <mergeCell ref="C31:S31"/>
+    <mergeCell ref="B32:S32"/>
+    <mergeCell ref="B33:S33"/>
+    <mergeCell ref="B34:S34"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -11953,21 +14121,21 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="2:14" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="191" t="s">
+      <c r="B5" s="291" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="191"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
+      <c r="C5" s="291"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="291"/>
+      <c r="F5" s="291"/>
+      <c r="G5" s="291"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
+      <c r="J5" s="291"/>
+      <c r="K5" s="291"/>
+      <c r="L5" s="291"/>
+      <c r="M5" s="291"/>
+      <c r="N5" s="291"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C6" s="6"/>
@@ -12345,14 +14513,14 @@
       <c r="G25" s="28"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="192" t="s">
+      <c r="B26" s="292" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="192"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="192"/>
-      <c r="G26" s="192"/>
+      <c r="C26" s="292"/>
+      <c r="D26" s="292"/>
+      <c r="E26" s="292"/>
+      <c r="F26" s="292"/>
+      <c r="G26" s="292"/>
     </row>
   </sheetData>
   <autoFilter ref="B7:G7" xr:uid="{D24798CD-838D-40FE-BB76-9E453F83021F}"/>
@@ -12399,12 +14567,12 @@
       <c r="D2"/>
     </row>
     <row r="3" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="193" t="str">
+      <c r="B3" s="293" t="str">
         <f>'Consolidado- Comber'!B5</f>
         <v>CRONOGRAMA FECHAMENTO - SETEMBRO 2026</v>
       </c>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
       <c r="E3" s="68"/>
     </row>
     <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -13304,7 +15472,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC645651-9DDF-4CA8-8A3C-DBB4CA0C4E10}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O146"/>
@@ -13355,7 +15523,7 @@
     </row>
     <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="104" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C5" s="105"/>
       <c r="D5" s="105"/>
@@ -16898,32 +19066,32 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121"/>
-      <c r="B121" s="159">
+      <c r="B121" s="158">
         <v>7</v>
       </c>
-      <c r="C121" s="159" t="s">
+      <c r="C121" s="158" t="s">
         <v>121</v>
       </c>
-      <c r="D121" s="160" t="s">
+      <c r="D121" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="E121" s="161" t="s">
+      <c r="E121" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="F121" s="162" t="s">
+      <c r="F121" s="161" t="s">
         <v>99</v>
       </c>
       <c r="G121" s="43" t="str">
         <f>$O121&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O121,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
         <v>3º dia útil - 05/out</v>
       </c>
-      <c r="H121" s="182">
+      <c r="H121" s="181">
         <v>0.75</v>
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="65"/>
-      <c r="M121" s="182"/>
-      <c r="O121" s="189">
+      <c r="M121" s="181"/>
+      <c r="O121" s="188">
         <v>3</v>
       </c>
     </row>
@@ -16936,7 +19104,7 @@
         <v>105</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E122" s="47" t="s">
         <v>61</v>
@@ -16967,7 +19135,7 @@
         <v>109</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E123" s="47" t="s">
         <v>61</v>
@@ -16998,7 +19166,7 @@
         <v>110</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E124" s="47" t="s">
         <v>61</v>
@@ -17029,7 +19197,7 @@
         <v>111</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E125" s="47" t="s">
         <v>61</v>
@@ -17060,7 +19228,7 @@
         <v>112</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E126" s="47" t="s">
         <v>61</v>
@@ -17091,7 +19259,7 @@
         <v>113</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E127" s="47" t="s">
         <v>61</v>
@@ -17122,7 +19290,7 @@
         <v>115</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E128" s="47" t="s">
         <v>61</v>
@@ -17153,13 +19321,13 @@
         <v>105</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E129" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F129" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G129" s="43" t="str">
         <f>$O129&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O129,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17184,13 +19352,13 @@
         <v>109</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E130" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F130" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G130" s="43" t="str">
         <f>$O130&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O130,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17215,13 +19383,13 @@
         <v>110</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E131" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F131" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G131" s="43" t="str">
         <f>$O131&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O131,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17246,13 +19414,13 @@
         <v>111</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E132" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F132" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G132" s="43" t="str">
         <f>$O132&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O132,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17277,13 +19445,13 @@
         <v>112</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E133" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F133" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G133" s="43" t="str">
         <f>$O133&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O133,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17308,13 +19476,13 @@
         <v>113</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E134" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F134" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G134" s="43" t="str">
         <f>$O134&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O134,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17339,13 +19507,13 @@
         <v>115</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E135" s="47" t="s">
         <v>61</v>
       </c>
       <c r="F135" s="47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G135" s="43" t="str">
         <f>$O135&amp;"º dia útil - "&amp;TEXT(_xlfn.XLOOKUP($A$1&amp;"|"&amp;$O135,ListBox!$H:$H,ListBox!$A:$A,0,0),"DD/MMM")</f>
@@ -17362,300 +19530,300 @@
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B136" s="167">
+      <c r="B136" s="166">
         <v>1</v>
       </c>
-      <c r="C136" s="165" t="s">
+      <c r="C136" s="164" t="s">
         <v>105</v>
       </c>
-      <c r="D136" s="169" t="s">
+      <c r="D136" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E136" s="167" t="s">
+      <c r="E136" s="166" t="s">
         <v>123</v>
       </c>
-      <c r="F136" s="170" t="s">
+      <c r="F136" s="169" t="s">
         <v>124</v>
       </c>
-      <c r="G136" s="181" t="s">
+      <c r="G136" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H136" s="184">
+      <c r="H136" s="183">
         <v>0.75</v>
       </c>
-      <c r="J136" s="186"/>
-      <c r="K136" s="170"/>
-      <c r="M136" s="170"/>
-      <c r="O136" s="170"/>
+      <c r="J136" s="185"/>
+      <c r="K136" s="169"/>
+      <c r="M136" s="169"/>
+      <c r="O136" s="169"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B137" s="163">
+      <c r="B137" s="162">
         <v>5</v>
       </c>
       <c r="C137" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="D137" s="169" t="s">
+      <c r="D137" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E137" s="167" t="s">
+      <c r="E137" s="166" t="s">
         <v>123</v>
       </c>
-      <c r="F137" s="163" t="s">
+      <c r="F137" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="G137" s="181" t="s">
+      <c r="G137" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H137" s="184">
+      <c r="H137" s="183">
         <v>0.75</v>
       </c>
-      <c r="J137" s="186"/>
-      <c r="K137" s="163"/>
-      <c r="M137" s="170"/>
-      <c r="O137" s="170"/>
+      <c r="J137" s="185"/>
+      <c r="K137" s="162"/>
+      <c r="M137" s="169"/>
+      <c r="O137" s="169"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B138" s="171">
+      <c r="B138" s="170">
         <v>7</v>
       </c>
-      <c r="C138" s="172" t="s">
+      <c r="C138" s="171" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="169" t="s">
+      <c r="D138" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E138" s="170" t="s">
+      <c r="E138" s="169" t="s">
         <v>123</v>
       </c>
-      <c r="F138" s="173" t="s">
+      <c r="F138" s="172" t="s">
         <v>124</v>
       </c>
-      <c r="G138" s="181" t="s">
+      <c r="G138" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H138" s="184">
+      <c r="H138" s="183">
         <v>0.75</v>
       </c>
-      <c r="J138" s="186"/>
-      <c r="K138" s="171"/>
-      <c r="M138" s="163"/>
-      <c r="O138" s="163"/>
+      <c r="J138" s="185"/>
+      <c r="K138" s="170"/>
+      <c r="M138" s="162"/>
+      <c r="O138" s="162"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B139" s="167">
+      <c r="B139" s="166">
         <v>10</v>
       </c>
-      <c r="C139" s="165" t="s">
+      <c r="C139" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="D139" s="169" t="s">
+      <c r="D139" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E139" s="167" t="s">
+      <c r="E139" s="166" t="s">
         <v>123</v>
       </c>
-      <c r="F139" s="170" t="s">
+      <c r="F139" s="169" t="s">
         <v>124</v>
       </c>
-      <c r="G139" s="181" t="s">
+      <c r="G139" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H139" s="183">
+      <c r="H139" s="182">
         <v>0.75</v>
       </c>
-      <c r="J139" s="186"/>
-      <c r="K139" s="170"/>
-      <c r="M139" s="171"/>
-      <c r="O139" s="171"/>
+      <c r="J139" s="185"/>
+      <c r="K139" s="169"/>
+      <c r="M139" s="170"/>
+      <c r="O139" s="170"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B140" s="170">
+      <c r="B140" s="169">
         <v>6</v>
       </c>
       <c r="C140" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="D140" s="166" t="s">
+      <c r="D140" s="165" t="s">
         <v>122</v>
       </c>
-      <c r="E140" s="174" t="s">
+      <c r="E140" s="173" t="s">
         <v>123</v>
       </c>
-      <c r="F140" s="174" t="s">
+      <c r="F140" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="G140" s="181" t="s">
+      <c r="G140" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H140" s="185">
+      <c r="H140" s="184">
         <v>0.75</v>
       </c>
-      <c r="J140" s="186"/>
-      <c r="K140" s="167"/>
-      <c r="L140" s="164"/>
-      <c r="M140" s="163"/>
-      <c r="O140" s="163"/>
+      <c r="J140" s="185"/>
+      <c r="K140" s="166"/>
+      <c r="L140" s="163"/>
+      <c r="M140" s="162"/>
+      <c r="O140" s="162"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B141" s="164">
+      <c r="B141" s="163">
         <v>9</v>
       </c>
-      <c r="C141" s="165" t="s">
+      <c r="C141" s="164" t="s">
         <v>126</v>
       </c>
-      <c r="D141" s="169" t="s">
+      <c r="D141" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E141" s="170" t="s">
+      <c r="E141" s="169" t="s">
         <v>123</v>
       </c>
-      <c r="F141" s="174" t="s">
+      <c r="F141" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="G141" s="181" t="s">
+      <c r="G141" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H141" s="184">
+      <c r="H141" s="183">
         <v>0.75</v>
       </c>
-      <c r="J141" s="187"/>
-      <c r="K141" s="170"/>
-      <c r="M141" s="171"/>
-      <c r="O141" s="171"/>
+      <c r="J141" s="186"/>
+      <c r="K141" s="169"/>
+      <c r="M141" s="170"/>
+      <c r="O141" s="170"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B142" s="177">
+      <c r="B142" s="176">
         <v>12</v>
       </c>
-      <c r="C142" s="175" t="s">
+      <c r="C142" s="174" t="s">
         <v>117</v>
       </c>
-      <c r="D142" s="166" t="s">
+      <c r="D142" s="165" t="s">
         <v>122</v>
       </c>
-      <c r="E142" s="174" t="s">
+      <c r="E142" s="173" t="s">
         <v>123</v>
       </c>
-      <c r="F142" s="174" t="s">
+      <c r="F142" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="G142" s="181" t="s">
+      <c r="G142" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H142" s="183">
+      <c r="H142" s="182">
         <v>0.75</v>
       </c>
-      <c r="J142" s="188"/>
-      <c r="K142" s="163"/>
-      <c r="M142" s="163"/>
-      <c r="O142" s="163"/>
-    </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B143" s="163">
+      <c r="J142" s="187"/>
+      <c r="K142" s="162"/>
+      <c r="M142" s="162"/>
+      <c r="O142" s="162"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B143" s="162">
         <v>13</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D143" s="169" t="s">
+      <c r="D143" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E143" s="167" t="s">
+      <c r="E143" s="166" t="s">
         <v>123</v>
       </c>
-      <c r="F143" s="170" t="s">
+      <c r="F143" s="169" t="s">
         <v>124</v>
       </c>
-      <c r="G143" s="181" t="s">
+      <c r="G143" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H143" s="185">
+      <c r="H143" s="184">
         <v>0.75</v>
       </c>
-      <c r="J143" s="186"/>
-      <c r="K143" s="171"/>
-      <c r="M143" s="171"/>
-    </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="J143" s="185"/>
+      <c r="K143" s="170"/>
+      <c r="M143" s="170"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B144" s="5">
         <v>15</v>
       </c>
-      <c r="C144" s="167" t="s">
+      <c r="C144" s="166" t="s">
         <v>128</v>
       </c>
-      <c r="D144" s="169" t="s">
+      <c r="D144" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="E144" s="170" t="s">
+      <c r="E144" s="169" t="s">
         <v>123</v>
       </c>
-      <c r="F144" s="174" t="s">
+      <c r="F144" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="G144" s="181" t="s">
+      <c r="G144" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H144" s="184">
+      <c r="H144" s="183">
         <v>0.75</v>
       </c>
-      <c r="J144" s="186"/>
-      <c r="K144" s="170"/>
-      <c r="M144" s="170"/>
+      <c r="J144" s="185"/>
+      <c r="K144" s="169"/>
+      <c r="M144" s="169"/>
     </row>
     <row r="145" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B145" s="164">
+      <c r="B145" s="163">
         <v>14</v>
       </c>
-      <c r="C145" s="163" t="s">
+      <c r="C145" s="162" t="s">
         <v>129</v>
       </c>
-      <c r="D145" s="180" t="s">
+      <c r="D145" s="179" t="s">
         <v>122</v>
       </c>
-      <c r="E145" s="170" t="s">
+      <c r="E145" s="169" t="s">
         <v>123</v>
       </c>
-      <c r="F145" s="174" t="s">
+      <c r="F145" s="173" t="s">
         <v>124</v>
       </c>
-      <c r="G145" s="181" t="s">
+      <c r="G145" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H145" s="184">
+      <c r="H145" s="183">
         <v>0.75</v>
       </c>
-      <c r="J145" s="186"/>
-      <c r="K145" s="170"/>
-      <c r="M145" s="163"/>
-      <c r="O145" s="163"/>
+      <c r="J145" s="185"/>
+      <c r="K145" s="169"/>
+      <c r="M145" s="162"/>
+      <c r="O145" s="162"/>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B146" s="168">
+      <c r="B146" s="167">
         <v>16</v>
       </c>
-      <c r="C146" s="179" t="s">
+      <c r="C146" s="178" t="s">
         <v>130</v>
       </c>
-      <c r="D146" s="178" t="s">
+      <c r="D146" s="177" t="s">
         <v>122</v>
       </c>
-      <c r="E146" s="163" t="s">
+      <c r="E146" s="162" t="s">
         <v>123</v>
       </c>
-      <c r="F146" s="176" t="s">
+      <c r="F146" s="175" t="s">
         <v>124</v>
       </c>
-      <c r="G146" s="181" t="s">
+      <c r="G146" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="H146" s="183">
+      <c r="H146" s="182">
         <v>0.75</v>
       </c>
-      <c r="J146" s="187"/>
-      <c r="K146" s="163"/>
-      <c r="M146" s="168"/>
-      <c r="O146" s="168"/>
+      <c r="J146" s="186"/>
+      <c r="K146" s="162"/>
+      <c r="M146" s="167"/>
+      <c r="O146" s="167"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:O146" xr:uid="{DC645651-9DDF-4CA8-8A3C-DBB4CA0C4E10}"/>
@@ -17710,18 +19878,18 @@
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="2:14" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="191" t="s">
+      <c r="B5" s="291" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="191"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
+      <c r="C5" s="291"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="291"/>
+      <c r="F5" s="291"/>
+      <c r="G5" s="291"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
+      <c r="J5" s="291"/>
+      <c r="K5" s="291"/>
       <c r="L5" s="37"/>
       <c r="M5" s="37"/>
       <c r="N5" s="37"/>
@@ -18123,18 +20291,18 @@
       <c r="K25" s="26"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="194" t="s">
+      <c r="B26" s="294" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="194"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="194"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="194"/>
+      <c r="C26" s="294"/>
+      <c r="D26" s="294"/>
+      <c r="E26" s="294"/>
+      <c r="F26" s="294"/>
+      <c r="G26" s="294"/>
+      <c r="H26" s="294"/>
+      <c r="I26" s="294"/>
+      <c r="J26" s="294"/>
+      <c r="K26" s="294"/>
     </row>
   </sheetData>
   <autoFilter ref="B7:K7" xr:uid="{12A5BBDB-FE10-4E38-92BC-480072D95872}"/>
@@ -30824,15 +32992,15 @@
       <c r="AJ1" s="112"/>
     </row>
     <row r="2" spans="2:36" ht="21" x14ac:dyDescent="0.25">
-      <c r="B2" s="195" t="str">
+      <c r="B2" s="295" t="str">
         <f>"DETALHAMENTO DAS ENTREGAS   ·   "&amp;_xlfn.TEXTAFTER('Consolidado- Comber'!$B$5,"- ")</f>
         <v>DETALHAMENTO DAS ENTREGAS   ·   SETEMBRO 2026</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
       <c r="I2" s="112"/>
       <c r="J2" s="112"/>
       <c r="K2" s="112"/>
@@ -30863,14 +33031,14 @@
       <c r="AJ2" s="112"/>
     </row>
     <row r="3" spans="2:36" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="296" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
       <c r="I3" s="112"/>
       <c r="J3" s="112"/>
       <c r="K3" s="112"/>
@@ -31015,13 +33183,13 @@
       <c r="AJ6" s="112"/>
     </row>
     <row r="7" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="199" t="str">
+      <c r="B7" s="298" t="str">
         <f>$C$33&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$33,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Fechamento das áreas operacionais e validação fiscal"</f>
         <v>1º DIA ÚTIL   ·   01/out   ·   Fechamento das áreas operacionais e validação fiscal</v>
       </c>
-      <c r="C7" s="200"/>
-      <c r="D7" s="200"/>
-      <c r="E7" s="200"/>
+      <c r="C7" s="299"/>
+      <c r="D7" s="299"/>
+      <c r="E7" s="299"/>
       <c r="F7" s="116">
         <f>SUM(F8:F12)</f>
         <v>35</v>
@@ -31211,14 +33379,14 @@
     </row>
     <row r="11" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="130" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C11" s="119" t="str">
         <f>B11</f>
         <v>Escrita Fiscal</v>
       </c>
       <c r="D11" s="120" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E11" s="121" t="s">
         <v>178</v>
@@ -31260,12 +33428,12 @@
       <c r="AI11" s="112"/>
       <c r="AJ11" s="112"/>
     </row>
-    <row r="12" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="138" t="s">
         <v>61</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D12" s="120" t="s">
         <v>189</v>
@@ -31310,14 +33478,14 @@
       <c r="AI12" s="112"/>
       <c r="AJ12" s="112"/>
     </row>
-    <row r="13" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="203" t="str">
+    <row r="13" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="300" t="str">
         <f>$C$34&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$34,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Correção dos apontamentos da validação fiscal"</f>
         <v>2º DIA ÚTIL   ·   02/out   ·   Correção dos apontamentos da validação fiscal</v>
       </c>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
+      <c r="C13" s="301"/>
+      <c r="D13" s="301"/>
+      <c r="E13" s="301"/>
       <c r="F13" s="136">
         <f>SUM(F14:F14)</f>
         <v>7</v>
@@ -31355,15 +33523,15 @@
       <c r="AI13" s="112"/>
       <c r="AJ13" s="112"/>
     </row>
-    <row r="14" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="138" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="119" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D14" s="120" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="E14" s="121" t="s">
         <v>178</v>
@@ -31406,13 +33574,13 @@
       <c r="AJ14" s="112"/>
     </row>
     <row r="15" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="201" t="str">
+      <c r="B15" s="302" t="str">
         <f>$C$35&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$35,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Financeiro, tesouraria e patrimônio"</f>
         <v>3º DIA ÚTIL   ·   05/out   ·   Financeiro, tesouraria e patrimônio</v>
       </c>
-      <c r="C15" s="202"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
+      <c r="C15" s="303"/>
+      <c r="D15" s="303"/>
+      <c r="E15" s="303"/>
       <c r="F15" s="131">
         <f>SUM(F16:F19)</f>
         <v>46</v>
@@ -31500,7 +33668,7 @@
       <c r="AI16" s="112"/>
       <c r="AJ16" s="112"/>
     </row>
-    <row r="17" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="134" t="s">
         <v>55</v>
       </c>
@@ -31550,7 +33718,7 @@
       <c r="AI17" s="112"/>
       <c r="AJ17" s="112"/>
     </row>
-    <row r="18" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="133" t="s">
         <v>55</v>
       </c>
@@ -31600,7 +33768,7 @@
       <c r="AI18" s="112"/>
       <c r="AJ18" s="112"/>
     </row>
-    <row r="19" spans="2:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="135" t="s">
         <v>185</v>
       </c>
@@ -31651,13 +33819,13 @@
       <c r="AJ19" s="112"/>
     </row>
     <row r="20" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="205" t="str">
+      <c r="B20" s="304" t="str">
         <f>$C$36&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$36,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Folha de pagamento"</f>
         <v>4º DIA ÚTIL   ·   06/out   ·   Folha de pagamento</v>
       </c>
-      <c r="C20" s="206"/>
-      <c r="D20" s="206"/>
-      <c r="E20" s="206"/>
+      <c r="C20" s="305"/>
+      <c r="D20" s="305"/>
+      <c r="E20" s="305"/>
       <c r="F20" s="139">
         <f>SUM(F21:F21)</f>
         <v>6</v>
@@ -31746,13 +33914,13 @@
       <c r="AJ21" s="112"/>
     </row>
     <row r="22" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="203" t="str">
+      <c r="B22" s="300" t="str">
         <f>$C$37&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$37,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Apuração de tributos"</f>
         <v>7º DIA ÚTIL   ·   09/out   ·   Apuração de tributos</v>
       </c>
-      <c r="C22" s="204"/>
-      <c r="D22" s="204"/>
-      <c r="E22" s="204"/>
+      <c r="C22" s="301"/>
+      <c r="D22" s="301"/>
+      <c r="E22" s="301"/>
       <c r="F22" s="136">
         <f>SUM(F23:F23)</f>
         <v>7</v>
@@ -31841,13 +34009,13 @@
       <c r="AJ23" s="112"/>
     </row>
     <row r="24" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="207" t="str">
+      <c r="B24" s="306" t="str">
         <f>$C$38&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$38,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Integração contábil"</f>
         <v>9º DIA ÚTIL   ·   14/out   ·   Integração contábil</v>
       </c>
-      <c r="C24" s="208"/>
-      <c r="D24" s="208"/>
-      <c r="E24" s="208"/>
+      <c r="C24" s="307"/>
+      <c r="D24" s="307"/>
+      <c r="E24" s="307"/>
       <c r="F24" s="142">
         <f>SUM(F25:F25)</f>
         <v>6</v>
@@ -31936,13 +34104,13 @@
       <c r="AJ25" s="112"/>
     </row>
     <row r="26" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="209" t="str">
+      <c r="B26" s="308" t="str">
         <f>$C$39&amp;"º DIA ÚTIL   ·   "&amp;TEXT(_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;$C$39,ListBox!$H:$H,ListBox!$A:$A,0,0),"dd/mmm")&amp;"   ·   Entrega do balancete fechado"</f>
         <v>15º DIA ÚTIL   ·   22/out   ·   Entrega do balancete fechado</v>
       </c>
-      <c r="C26" s="210"/>
-      <c r="D26" s="210"/>
-      <c r="E26" s="210"/>
+      <c r="C26" s="309"/>
+      <c r="D26" s="309"/>
+      <c r="E26" s="309"/>
       <c r="F26" s="145">
         <f>SUM(F27:F27)</f>
         <v>6</v>
@@ -31987,7 +34155,7 @@
       <c r="C27" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="190" t="s">
+      <c r="D27" s="189" t="s">
         <v>193</v>
       </c>
       <c r="E27" s="149" t="s">
@@ -32061,14 +34229,14 @@
       <c r="AJ28" s="112"/>
     </row>
     <row r="29" spans="1:36" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="198" t="s">
+      <c r="B29" s="297" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="196"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="196"/>
-      <c r="G29" s="196"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="191"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="191"/>
       <c r="I29" s="112"/>
       <c r="J29" s="112"/>
       <c r="K29" s="112"/>

--- a/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
+++ b/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
@@ -13119,14 +13119,14 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:S34"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="19" width="8.2" customWidth="1"/>
-    <col min="20" max="20" width="2.5" customWidth="1"/>
+    <col min="4" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="2.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -13215,26 +13215,6 @@
           <t xml:space="preserve">11º d.u.</t>
         </is>
       </c>
-      <c r="P5" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12º d.u.</t>
-        </is>
-      </c>
-      <c r="Q5" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13º d.u.</t>
-        </is>
-      </c>
-      <c r="R5" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14º d.u.</t>
-        </is>
-      </c>
-      <c r="S5" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15º d.u.</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="328" t="inlineStr">
@@ -13291,22 +13271,6 @@
         <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;11,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
         <v>46311</v>
       </c>
-      <c r="P6" s="332">
-        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;12,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
-        <v>46314</v>
-      </c>
-      <c r="Q6" s="332">
-        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;13,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
-        <v>46315</v>
-      </c>
-      <c r="R6" s="332">
-        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;14,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
-        <v>46316</v>
-      </c>
-      <c r="S6" s="332">
-        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;15,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
-        <v>46317</v>
-      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="330" t="inlineStr">
@@ -13362,22 +13326,6 @@
       <c r="O7" s="333" t="str">
         <f>LOWER(TEXT(O6,"ddd"))</f>
         <v>sex</v>
-      </c>
-      <c r="P7" s="333" t="str">
-        <f>LOWER(TEXT(P6,"ddd"))</f>
-        <v>seg</v>
-      </c>
-      <c r="Q7" s="333" t="str">
-        <f>LOWER(TEXT(Q6,"ddd"))</f>
-        <v>ter</v>
-      </c>
-      <c r="R7" s="333" t="str">
-        <f>LOWER(TEXT(R6,"ddd"))</f>
-        <v>qua</v>
-      </c>
-      <c r="S7" s="333" t="str">
-        <f>LOWER(TEXT(S6,"ddd"))</f>
-        <v>qui</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
@@ -13404,10 +13352,6 @@
       <c r="M9" s="336"/>
       <c r="N9" s="336"/>
       <c r="O9" s="336"/>
-      <c r="P9" s="336"/>
-      <c r="Q9" s="336"/>
-      <c r="R9" s="336"/>
-      <c r="S9" s="336"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="337" t="inlineStr">
@@ -13436,10 +13380,6 @@
       <c r="M10" s="340"/>
       <c r="N10" s="340"/>
       <c r="O10" s="340"/>
-      <c r="P10" s="340"/>
-      <c r="Q10" s="340"/>
-      <c r="R10" s="340"/>
-      <c r="S10" s="340"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="337" t="inlineStr">
@@ -13468,10 +13408,6 @@
       <c r="M11" s="340"/>
       <c r="N11" s="340"/>
       <c r="O11" s="340"/>
-      <c r="P11" s="340"/>
-      <c r="Q11" s="340"/>
-      <c r="R11" s="340"/>
-      <c r="S11" s="340"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="337" t="inlineStr">
@@ -13500,10 +13436,6 @@
       <c r="M12" s="340"/>
       <c r="N12" s="340"/>
       <c r="O12" s="340"/>
-      <c r="P12" s="340"/>
-      <c r="Q12" s="340"/>
-      <c r="R12" s="340"/>
-      <c r="S12" s="340"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="337" t="inlineStr">
@@ -13532,10 +13464,6 @@
       <c r="M13" s="340"/>
       <c r="N13" s="340"/>
       <c r="O13" s="340"/>
-      <c r="P13" s="340"/>
-      <c r="Q13" s="340"/>
-      <c r="R13" s="340"/>
-      <c r="S13" s="340"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="341" t="inlineStr">
@@ -13560,10 +13488,6 @@
       <c r="M14" s="343"/>
       <c r="N14" s="343"/>
       <c r="O14" s="343"/>
-      <c r="P14" s="343"/>
-      <c r="Q14" s="343"/>
-      <c r="R14" s="343"/>
-      <c r="S14" s="343"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="337" t="inlineStr">
@@ -13592,10 +13516,6 @@
       <c r="M15" s="340"/>
       <c r="N15" s="340"/>
       <c r="O15" s="340"/>
-      <c r="P15" s="340"/>
-      <c r="Q15" s="340"/>
-      <c r="R15" s="340"/>
-      <c r="S15" s="340"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="337" t="inlineStr">
@@ -13624,10 +13544,6 @@
       <c r="M16" s="340"/>
       <c r="N16" s="340"/>
       <c r="O16" s="340"/>
-      <c r="P16" s="340"/>
-      <c r="Q16" s="340"/>
-      <c r="R16" s="340"/>
-      <c r="S16" s="340"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="345" t="inlineStr">
@@ -13652,10 +13568,6 @@
       <c r="M17" s="347"/>
       <c r="N17" s="347"/>
       <c r="O17" s="347"/>
-      <c r="P17" s="347"/>
-      <c r="Q17" s="347"/>
-      <c r="R17" s="347"/>
-      <c r="S17" s="347"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="337" t="inlineStr">
@@ -13684,10 +13596,6 @@
       <c r="M18" s="340"/>
       <c r="N18" s="340"/>
       <c r="O18" s="340"/>
-      <c r="P18" s="340"/>
-      <c r="Q18" s="340"/>
-      <c r="R18" s="340"/>
-      <c r="S18" s="340"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="337" t="inlineStr">
@@ -13716,10 +13624,6 @@
       <c r="M19" s="340"/>
       <c r="N19" s="340"/>
       <c r="O19" s="340"/>
-      <c r="P19" s="340"/>
-      <c r="Q19" s="340"/>
-      <c r="R19" s="340"/>
-      <c r="S19" s="340"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="337" t="inlineStr">
@@ -13748,10 +13652,6 @@
       <c r="M20" s="340"/>
       <c r="N20" s="340"/>
       <c r="O20" s="340"/>
-      <c r="P20" s="340"/>
-      <c r="Q20" s="340"/>
-      <c r="R20" s="340"/>
-      <c r="S20" s="340"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="337" t="inlineStr">
@@ -13780,10 +13680,6 @@
       <c r="M21" s="340"/>
       <c r="N21" s="340"/>
       <c r="O21" s="340"/>
-      <c r="P21" s="340"/>
-      <c r="Q21" s="340"/>
-      <c r="R21" s="340"/>
-      <c r="S21" s="340"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="349" t="inlineStr">
@@ -13804,10 +13700,6 @@
       <c r="M22" s="351"/>
       <c r="N22" s="351"/>
       <c r="O22" s="351"/>
-      <c r="P22" s="351"/>
-      <c r="Q22" s="351"/>
-      <c r="R22" s="351"/>
-      <c r="S22" s="351"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="337" t="inlineStr">
@@ -13836,10 +13728,6 @@
       <c r="M23" s="340"/>
       <c r="N23" s="340"/>
       <c r="O23" s="340"/>
-      <c r="P23" s="340"/>
-      <c r="Q23" s="340"/>
-      <c r="R23" s="340"/>
-      <c r="S23" s="340"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="353" t="inlineStr">
@@ -13864,10 +13752,6 @@
       <c r="M24" s="355"/>
       <c r="N24" s="355"/>
       <c r="O24" s="355"/>
-      <c r="P24" s="355"/>
-      <c r="Q24" s="355"/>
-      <c r="R24" s="355"/>
-      <c r="S24" s="355"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="337" t="inlineStr">
@@ -13900,15 +13784,11 @@
       <c r="M25" s="340"/>
       <c r="N25" s="340"/>
       <c r="O25" s="340"/>
-      <c r="P25" s="340"/>
-      <c r="Q25" s="340"/>
-      <c r="R25" s="340"/>
-      <c r="S25" s="340"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apuração de PIS/COFINS</t>
+          <t xml:space="preserve">Apuração de PIS/COFINS (após o balancete)</t>
         </is>
       </c>
       <c r="C26" s="338" t="inlineStr">
@@ -13936,20 +13816,16 @@
           <t xml:space="preserve">···</t>
         </is>
       </c>
-      <c r="P26" s="360"/>
-      <c r="Q26" s="360"/>
-      <c r="R26" s="360"/>
-      <c r="S26" s="360"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="361" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 · Contabilidade</t>
+          <t xml:space="preserve">6 · Contabilidade e balancete fechado</t>
         </is>
       </c>
       <c r="C27" s="362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Começa com as apurações; libera o PIS/COFINS ao ser entregue</t>
+          <t xml:space="preserve">Começa com as apurações; o balancete fechado (10º d.u.) libera o PIS/COFINS</t>
         </is>
       </c>
       <c r="D27" s="363"/>
@@ -13964,15 +13840,11 @@
       <c r="M27" s="363"/>
       <c r="N27" s="363"/>
       <c r="O27" s="363"/>
-      <c r="P27" s="363"/>
-      <c r="Q27" s="363"/>
-      <c r="R27" s="363"/>
-      <c r="S27" s="363"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contabilidade</t>
+          <t xml:space="preserve">Contabilidade → balancete fechado</t>
         </is>
       </c>
       <c r="C28" s="338" t="inlineStr">
@@ -14000,67 +13872,38 @@
         </is>
       </c>
       <c r="O28" s="340"/>
-      <c r="P28" s="340"/>
-      <c r="Q28" s="340"/>
-      <c r="R28" s="340"/>
-      <c r="S28" s="340"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balancete fechado</t>
-        </is>
-      </c>
-      <c r="C29" s="338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joyce · Equipe Contábil</t>
-        </is>
-      </c>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
-      <c r="G29" s="340"/>
-      <c r="H29" s="340"/>
-      <c r="I29" s="340"/>
-      <c r="J29" s="340"/>
-      <c r="K29" s="340"/>
-      <c r="L29" s="340"/>
-      <c r="M29" s="340"/>
-      <c r="N29" s="340"/>
-      <c r="O29" s="340"/>
-      <c r="P29" s="340"/>
-      <c r="Q29" s="340"/>
-      <c r="R29" s="340"/>
-      <c r="S29" s="366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">◆</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="367" t="inlineStr">
+    </row>
+    <row r="29"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="B30" s="367" t="inlineStr">
         <is>
           <t xml:space="preserve">LEGENDA</t>
         </is>
       </c>
-      <c r="C31" s="368" t="inlineStr">
+      <c r="C30" s="368" t="inlineStr">
         <is>
           <t xml:space="preserve">◆  entrega / prazo final (até 18:00)     ■  período de execução     ···  depende de etapa anterior (sem prazo fixo)</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → apurações, contabilidade e financeiro (2º d.u.) → folha (4º d.u.) → impostos (7º d.u.) → contabilidade / balancete fechado (10º d.u.) → PIS/COFINS.</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → apurações, contabilidade e financeiro (2º d.u.) → folha (4º d.u.) → impostos (7º d.u.) → contabilidade (10º d.u.) → PIS/COFINS → balancete fechado (15º d.u.).</t>
+          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (2º d.u. + 5 = 7º d.u.). PIS/COFINS só é apurado depois da contabilidade finalizada.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (2º d.u. + 5 = 7º d.u.). PIS/COFINS só é apurado depois da contabilidade finalizada.</t>
+          <t xml:space="preserve">Em paralelo de 02/10 a 15/10: apurações fiscais, contabilidade, financeiro/patrimônio (02/10) e folha (06/10). A contabilidade recebe a folha e os impostos.</t>
         </is>
       </c>
     </row>
@@ -14072,19 +13915,20 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B2:S2"/>
-    <mergeCell ref="B3:S3"/>
-    <mergeCell ref="C9:S9"/>
-    <mergeCell ref="C14:S14"/>
-    <mergeCell ref="C17:S17"/>
-    <mergeCell ref="C22:S22"/>
-    <mergeCell ref="C24:S24"/>
-    <mergeCell ref="C27:S27"/>
-    <mergeCell ref="C31:S31"/>
-    <mergeCell ref="B32:S32"/>
-    <mergeCell ref="B33:S33"/>
-    <mergeCell ref="B34:S34"/>
+  <mergeCells count="13">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="C9:O9"/>
+    <mergeCell ref="C14:O14"/>
+    <mergeCell ref="C17:O17"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="C24:O24"/>
+    <mergeCell ref="C27:O27"/>
+    <mergeCell ref="C30:O30"/>
+    <mergeCell ref="B31:O31"/>
+    <mergeCell ref="B32:O32"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="B34:O34"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>

--- a/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
+++ b/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
@@ -881,7 +881,7 @@
     <numFmt numFmtId="165" formatCode="h:mm"/>
     <numFmt numFmtId="190" formatCode="dd/mmm"/>
   </numFmts>
-  <fonts count="116" x14ac:knownFonts="1">
+  <fonts count="115" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1483,6 +1483,13 @@
     </font>
     <font>
       <b/>
+      <sz val="8"/>
+      <color rgb="FF255E8E"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF2E75B6"/>
       <name val="Aptos"/>
@@ -1577,19 +1584,6 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF2F7D6E"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF2F7D6E"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF548235"/>
       <name val="Aptos"/>
@@ -1649,7 +1643,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1862,6 +1856,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC1D1DF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1892,18 +1892,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFEBE9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF2F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCFDCC6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1921,7 +1909,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="126">
+  <borders count="125">
     <border>
       <left/>
       <right/>
@@ -3033,6 +3021,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="hair">
+        <color rgb="FFD6DEE8"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD6DEE8"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD6DEE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -3179,32 +3180,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color rgb="FFD6DEE8"/>
-      </left>
-      <right style="hair">
-        <color rgb="FFD6DEE8"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FFD6DEE8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FFD6DEE8"/>
-      </left>
-      <right style="hair">
-        <color rgb="FFD6DEE8"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FFD6DEE8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -3276,7 +3251,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4255,8 +4230,8 @@
     <xf numFmtId="0" fontId="90" fillId="35" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="91" fillId="36" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4264,11 +4239,11 @@
     <xf numFmtId="0" fontId="93" fillId="0" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="36" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="37" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4276,11 +4251,11 @@
     <xf numFmtId="0" fontId="97" fillId="0" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="37" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="38" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4288,20 +4263,20 @@
     <xf numFmtId="0" fontId="101" fillId="0" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="38" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="39" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="39" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="40" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="40" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="105" fillId="41" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="106" fillId="42" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4309,25 +4284,22 @@
     <xf numFmtId="0" fontId="108" fillId="0" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="109" fillId="42" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="43" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="43" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="111" fillId="44" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="111" fillId="44" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="45" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13119,14 +13091,14 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O34"/>
+  <dimension ref="B2:Q34"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="2.5" customWidth="1"/>
+    <col min="4" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="2.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -13215,6 +13187,16 @@
           <t xml:space="preserve">11º d.u.</t>
         </is>
       </c>
+      <c r="P5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12º d.u.</t>
+        </is>
+      </c>
+      <c r="Q5" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13º d.u.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="328" t="inlineStr">
@@ -13271,6 +13253,14 @@
         <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;11,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
         <v>46311</v>
       </c>
+      <c r="P6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;12,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46314</v>
+      </c>
+      <c r="Q6" s="332">
+        <f>_xlfn.XLOOKUP('Consolidado- Comber'!$A$1&amp;"|"&amp;13,ListBox!$H:$H,ListBox!$A:$A,0,0)</f>
+        <v>46315</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="330" t="inlineStr">
@@ -13326,6 +13316,14 @@
       <c r="O7" s="333" t="str">
         <f>LOWER(TEXT(O6,"ddd"))</f>
         <v>sex</v>
+      </c>
+      <c r="P7" s="333" t="str">
+        <f>LOWER(TEXT(P6,"ddd"))</f>
+        <v>seg</v>
+      </c>
+      <c r="Q7" s="333" t="str">
+        <f>LOWER(TEXT(Q6,"ddd"))</f>
+        <v>ter</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1"/>
@@ -13352,6 +13350,8 @@
       <c r="M9" s="336"/>
       <c r="N9" s="336"/>
       <c r="O9" s="336"/>
+      <c r="P9" s="336"/>
+      <c r="Q9" s="336"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="337" t="inlineStr">
@@ -13380,6 +13380,8 @@
       <c r="M10" s="340"/>
       <c r="N10" s="340"/>
       <c r="O10" s="340"/>
+      <c r="P10" s="340"/>
+      <c r="Q10" s="340"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="337" t="inlineStr">
@@ -13408,6 +13410,8 @@
       <c r="M11" s="340"/>
       <c r="N11" s="340"/>
       <c r="O11" s="340"/>
+      <c r="P11" s="340"/>
+      <c r="Q11" s="340"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="337" t="inlineStr">
@@ -13436,6 +13440,8 @@
       <c r="M12" s="340"/>
       <c r="N12" s="340"/>
       <c r="O12" s="340"/>
+      <c r="P12" s="340"/>
+      <c r="Q12" s="340"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="337" t="inlineStr">
@@ -13464,16 +13470,18 @@
       <c r="M13" s="340"/>
       <c r="N13" s="340"/>
       <c r="O13" s="340"/>
+      <c r="P13" s="340"/>
+      <c r="Q13" s="340"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 · Trava e validação fiscal</t>
+          <t xml:space="preserve">2 · Trava, validação fiscal e correções</t>
         </is>
       </c>
       <c r="C14" s="342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema travado; o fiscal valida e as áreas corrigem no mesmo dia</t>
+          <t xml:space="preserve">Sistema travado no 1º d.u.; o time Comber corrige do 1º ao 2º d.u.</t>
         </is>
       </c>
       <c r="D14" s="343"/>
@@ -13488,6 +13496,8 @@
       <c r="M14" s="343"/>
       <c r="N14" s="343"/>
       <c r="O14" s="343"/>
+      <c r="P14" s="343"/>
+      <c r="Q14" s="343"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="337" t="inlineStr">
@@ -13516,11 +13526,13 @@
       <c r="M15" s="340"/>
       <c r="N15" s="340"/>
       <c r="O15" s="340"/>
+      <c r="P15" s="340"/>
+      <c r="Q15" s="340"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dia das correções</t>
+          <t xml:space="preserve">Correções (time Comber)</t>
         </is>
       </c>
       <c r="C16" s="338" t="inlineStr">
@@ -13529,12 +13541,16 @@
         </is>
       </c>
       <c r="D16" s="340"/>
-      <c r="E16" s="344" t="inlineStr">
+      <c r="E16" s="345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">início</t>
+        </is>
+      </c>
+      <c r="F16" s="344" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="F16" s="340"/>
       <c r="G16" s="340"/>
       <c r="H16" s="340"/>
       <c r="I16" s="340"/>
@@ -13544,30 +13560,34 @@
       <c r="M16" s="340"/>
       <c r="N16" s="340"/>
       <c r="O16" s="340"/>
+      <c r="P16" s="340"/>
+      <c r="Q16" s="340"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="345" t="inlineStr">
+      <c r="B17" s="346" t="inlineStr">
         <is>
           <t xml:space="preserve">3 · Financeiro e patrimônio</t>
         </is>
       </c>
-      <c r="C17" s="346" t="inlineStr">
+      <c r="C17" s="347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entregas no dia em que começam apurações e contabilidade</t>
+          <t xml:space="preserve">Entregas no dia em que começam apurações e contabilidade (3º d.u.)</t>
         </is>
       </c>
-      <c r="D17" s="347"/>
-      <c r="E17" s="347"/>
-      <c r="F17" s="347"/>
-      <c r="G17" s="347"/>
-      <c r="H17" s="347"/>
-      <c r="I17" s="347"/>
-      <c r="J17" s="347"/>
-      <c r="K17" s="347"/>
-      <c r="L17" s="347"/>
-      <c r="M17" s="347"/>
-      <c r="N17" s="347"/>
-      <c r="O17" s="347"/>
+      <c r="D17" s="348"/>
+      <c r="E17" s="348"/>
+      <c r="F17" s="348"/>
+      <c r="G17" s="348"/>
+      <c r="H17" s="348"/>
+      <c r="I17" s="348"/>
+      <c r="J17" s="348"/>
+      <c r="K17" s="348"/>
+      <c r="L17" s="348"/>
+      <c r="M17" s="348"/>
+      <c r="N17" s="348"/>
+      <c r="O17" s="348"/>
+      <c r="P17" s="348"/>
+      <c r="Q17" s="348"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="337" t="inlineStr">
@@ -13582,12 +13602,12 @@
       </c>
       <c r="D18" s="340"/>
       <c r="E18" s="340"/>
-      <c r="F18" s="348" t="inlineStr">
+      <c r="F18" s="340"/>
+      <c r="G18" s="349" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="G18" s="340"/>
       <c r="H18" s="340"/>
       <c r="I18" s="340"/>
       <c r="J18" s="340"/>
@@ -13596,6 +13616,8 @@
       <c r="M18" s="340"/>
       <c r="N18" s="340"/>
       <c r="O18" s="340"/>
+      <c r="P18" s="340"/>
+      <c r="Q18" s="340"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="337" t="inlineStr">
@@ -13610,12 +13632,12 @@
       </c>
       <c r="D19" s="340"/>
       <c r="E19" s="340"/>
-      <c r="F19" s="348" t="inlineStr">
+      <c r="F19" s="340"/>
+      <c r="G19" s="349" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="G19" s="340"/>
       <c r="H19" s="340"/>
       <c r="I19" s="340"/>
       <c r="J19" s="340"/>
@@ -13624,6 +13646,8 @@
       <c r="M19" s="340"/>
       <c r="N19" s="340"/>
       <c r="O19" s="340"/>
+      <c r="P19" s="340"/>
+      <c r="Q19" s="340"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="337" t="inlineStr">
@@ -13638,12 +13662,12 @@
       </c>
       <c r="D20" s="340"/>
       <c r="E20" s="340"/>
-      <c r="F20" s="348" t="inlineStr">
+      <c r="F20" s="340"/>
+      <c r="G20" s="349" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="G20" s="340"/>
       <c r="H20" s="340"/>
       <c r="I20" s="340"/>
       <c r="J20" s="340"/>
@@ -13652,6 +13676,8 @@
       <c r="M20" s="340"/>
       <c r="N20" s="340"/>
       <c r="O20" s="340"/>
+      <c r="P20" s="340"/>
+      <c r="Q20" s="340"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="337" t="inlineStr">
@@ -13666,12 +13692,12 @@
       </c>
       <c r="D21" s="340"/>
       <c r="E21" s="340"/>
-      <c r="F21" s="348" t="inlineStr">
+      <c r="F21" s="340"/>
+      <c r="G21" s="349" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="G21" s="340"/>
       <c r="H21" s="340"/>
       <c r="I21" s="340"/>
       <c r="J21" s="340"/>
@@ -13680,26 +13706,30 @@
       <c r="M21" s="340"/>
       <c r="N21" s="340"/>
       <c r="O21" s="340"/>
+      <c r="P21" s="340"/>
+      <c r="Q21" s="340"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="349" t="inlineStr">
+      <c r="B22" s="350" t="inlineStr">
         <is>
           <t xml:space="preserve">4 · Folha de pagamento</t>
         </is>
       </c>
-      <c r="C22" s="350"/>
-      <c r="D22" s="351"/>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
-      <c r="G22" s="351"/>
-      <c r="H22" s="351"/>
-      <c r="I22" s="351"/>
-      <c r="J22" s="351"/>
-      <c r="K22" s="351"/>
-      <c r="L22" s="351"/>
-      <c r="M22" s="351"/>
-      <c r="N22" s="351"/>
-      <c r="O22" s="351"/>
+      <c r="C22" s="351"/>
+      <c r="D22" s="352"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
+      <c r="G22" s="352"/>
+      <c r="H22" s="352"/>
+      <c r="I22" s="352"/>
+      <c r="J22" s="352"/>
+      <c r="K22" s="352"/>
+      <c r="L22" s="352"/>
+      <c r="M22" s="352"/>
+      <c r="N22" s="352"/>
+      <c r="O22" s="352"/>
+      <c r="P22" s="352"/>
+      <c r="Q22" s="352"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="337" t="inlineStr">
@@ -13716,7 +13746,7 @@
       <c r="E23" s="340"/>
       <c r="F23" s="340"/>
       <c r="G23" s="340"/>
-      <c r="H23" s="352" t="inlineStr">
+      <c r="H23" s="353" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
@@ -13728,30 +13758,34 @@
       <c r="M23" s="340"/>
       <c r="N23" s="340"/>
       <c r="O23" s="340"/>
+      <c r="P23" s="340"/>
+      <c r="Q23" s="340"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="353" t="inlineStr">
+      <c r="B24" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">5 · Apurações fiscais</t>
         </is>
       </c>
-      <c r="C24" s="354" t="inlineStr">
+      <c r="C24" s="355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrega 5 dias úteis após o início das apurações</t>
+          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações</t>
         </is>
       </c>
-      <c r="D24" s="355"/>
-      <c r="E24" s="355"/>
-      <c r="F24" s="355"/>
-      <c r="G24" s="355"/>
-      <c r="H24" s="355"/>
-      <c r="I24" s="355"/>
-      <c r="J24" s="355"/>
-      <c r="K24" s="355"/>
-      <c r="L24" s="355"/>
-      <c r="M24" s="355"/>
-      <c r="N24" s="355"/>
-      <c r="O24" s="355"/>
+      <c r="D24" s="356"/>
+      <c r="E24" s="356"/>
+      <c r="F24" s="356"/>
+      <c r="G24" s="356"/>
+      <c r="H24" s="356"/>
+      <c r="I24" s="356"/>
+      <c r="J24" s="356"/>
+      <c r="K24" s="356"/>
+      <c r="L24" s="356"/>
+      <c r="M24" s="356"/>
+      <c r="N24" s="356"/>
+      <c r="O24" s="356"/>
+      <c r="P24" s="356"/>
+      <c r="Q24" s="356"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="337" t="inlineStr">
@@ -13766,29 +13800,31 @@
       </c>
       <c r="D25" s="340"/>
       <c r="E25" s="340"/>
-      <c r="F25" s="356" t="inlineStr">
+      <c r="F25" s="340"/>
+      <c r="G25" s="357" t="inlineStr">
         <is>
           <t xml:space="preserve">início</t>
         </is>
       </c>
-      <c r="G25" s="357"/>
-      <c r="H25" s="357"/>
-      <c r="I25" s="357"/>
-      <c r="J25" s="357"/>
-      <c r="K25" s="358" t="inlineStr">
+      <c r="H25" s="358"/>
+      <c r="I25" s="358"/>
+      <c r="J25" s="358"/>
+      <c r="K25" s="358"/>
+      <c r="L25" s="359" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="L25" s="340"/>
       <c r="M25" s="340"/>
       <c r="N25" s="340"/>
       <c r="O25" s="340"/>
+      <c r="P25" s="340"/>
+      <c r="Q25" s="340"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apuração de PIS/COFINS (após o balancete)</t>
+          <t xml:space="preserve">PIS/COFINS finalizado</t>
         </is>
       </c>
       <c r="C26" s="338" t="inlineStr">
@@ -13806,40 +13842,40 @@
       <c r="K26" s="340"/>
       <c r="L26" s="340"/>
       <c r="M26" s="340"/>
-      <c r="N26" s="359" t="inlineStr">
+      <c r="N26" s="340"/>
+      <c r="O26" s="359" t="inlineStr">
         <is>
-          <t xml:space="preserve">após ▸</t>
+          <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="O26" s="360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">···</t>
-        </is>
-      </c>
+      <c r="P26" s="340"/>
+      <c r="Q26" s="340"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="361" t="inlineStr">
+      <c r="B27" s="360" t="inlineStr">
         <is>
           <t xml:space="preserve">6 · Contabilidade e balancete fechado</t>
         </is>
       </c>
-      <c r="C27" s="362" t="inlineStr">
+      <c r="C27" s="361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Começa com as apurações; o balancete fechado (10º d.u.) libera o PIS/COFINS</t>
+          <t xml:space="preserve">Começa no 3º d.u. e termina com o balancete fechado</t>
         </is>
       </c>
-      <c r="D27" s="363"/>
-      <c r="E27" s="363"/>
-      <c r="F27" s="363"/>
-      <c r="G27" s="363"/>
-      <c r="H27" s="363"/>
-      <c r="I27" s="363"/>
-      <c r="J27" s="363"/>
-      <c r="K27" s="363"/>
-      <c r="L27" s="363"/>
-      <c r="M27" s="363"/>
-      <c r="N27" s="363"/>
-      <c r="O27" s="363"/>
+      <c r="D27" s="362"/>
+      <c r="E27" s="362"/>
+      <c r="F27" s="362"/>
+      <c r="G27" s="362"/>
+      <c r="H27" s="362"/>
+      <c r="I27" s="362"/>
+      <c r="J27" s="362"/>
+      <c r="K27" s="362"/>
+      <c r="L27" s="362"/>
+      <c r="M27" s="362"/>
+      <c r="N27" s="362"/>
+      <c r="O27" s="362"/>
+      <c r="P27" s="362"/>
+      <c r="Q27" s="362"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="337" t="inlineStr">
@@ -13854,61 +13890,63 @@
       </c>
       <c r="D28" s="340"/>
       <c r="E28" s="340"/>
-      <c r="F28" s="364" t="inlineStr">
+      <c r="F28" s="340"/>
+      <c r="G28" s="363" t="inlineStr">
         <is>
           <t xml:space="preserve">início</t>
         </is>
       </c>
-      <c r="G28" s="365"/>
-      <c r="H28" s="365"/>
-      <c r="I28" s="365"/>
-      <c r="J28" s="365"/>
-      <c r="K28" s="365"/>
-      <c r="L28" s="365"/>
-      <c r="M28" s="365"/>
-      <c r="N28" s="366" t="inlineStr">
+      <c r="H28" s="364"/>
+      <c r="I28" s="364"/>
+      <c r="J28" s="364"/>
+      <c r="K28" s="364"/>
+      <c r="L28" s="364"/>
+      <c r="M28" s="364"/>
+      <c r="N28" s="364"/>
+      <c r="O28" s="364"/>
+      <c r="P28" s="364"/>
+      <c r="Q28" s="365" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
-      <c r="O28" s="340"/>
     </row>
     <row r="29"/>
     <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="367" t="inlineStr">
+      <c r="B30" s="366" t="inlineStr">
         <is>
           <t xml:space="preserve">LEGENDA</t>
         </is>
       </c>
-      <c r="C30" s="368" t="inlineStr">
+      <c r="C30" s="367" t="inlineStr">
         <is>
           <t xml:space="preserve">◆  entrega / prazo final (até 18:00)     ■  período de execução     ···  depende de etapa anterior (sem prazo fixo)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="369" t="inlineStr">
+      <c r="B31" s="368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → apurações, contabilidade e financeiro (2º d.u.) → folha (4º d.u.) → impostos (7º d.u.) → contabilidade / balancete fechado (10º d.u.) → PIS/COFINS.</t>
+          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → correções do time Comber (1º ao 2º d.u.) → apurações, contabilidade e financeiro (3º d.u.) → folha (4º d.u.) → impostos (8º d.u.) → PIS/COFINS (11º d.u.) → balancete fechado (13º d.u.).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="369" t="inlineStr">
+      <c r="B32" s="368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (2º d.u. + 5 = 7º d.u.). PIS/COFINS só é apurado depois da contabilidade finalizada.</t>
+          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (3º d.u. + 5 = 8º d.u.). PIS/COFINS finalizado no 11º d.u.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="369" t="inlineStr">
+      <c r="B33" s="368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em paralelo de 02/10 a 15/10: apurações fiscais, contabilidade, financeiro/patrimônio (02/10) e folha (06/10). A contabilidade recebe a folha e os impostos.</t>
+          <t xml:space="preserve">Em paralelo do 3º ao 13º d.u.: apurações fiscais, contabilidade, financeiro/patrimônio (3º d.u.), folha (4º d.u.) e PIS/COFINS (11º d.u.). A contabilidade recebe a folha e os impostos.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="369" t="inlineStr">
+      <c r="B34" s="368" t="inlineStr">
         <is>
           <t xml:space="preserve">Feriados e fins de semana não entram na contagem: as colunas mostram apenas dias úteis.</t>
         </is>
@@ -13916,19 +13954,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="C9:O9"/>
-    <mergeCell ref="C14:O14"/>
-    <mergeCell ref="C17:O17"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="C24:O24"/>
-    <mergeCell ref="C27:O27"/>
-    <mergeCell ref="C30:O30"/>
-    <mergeCell ref="B31:O31"/>
-    <mergeCell ref="B32:O32"/>
-    <mergeCell ref="B33:O33"/>
-    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="C9:Q9"/>
+    <mergeCell ref="C14:Q14"/>
+    <mergeCell ref="C17:Q17"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="C24:Q24"/>
+    <mergeCell ref="C27:Q27"/>
+    <mergeCell ref="C30:Q30"/>
+    <mergeCell ref="B31:Q31"/>
+    <mergeCell ref="B32:Q32"/>
+    <mergeCell ref="B33:Q33"/>
+    <mergeCell ref="B34:Q34"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>

--- a/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
+++ b/12. Ficha de Controle Grupo Comber - SETEMBRO 2026.xlsx
@@ -13769,7 +13769,7 @@
       </c>
       <c r="C24" s="355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações</t>
+          <t xml:space="preserve">Impostos entregues no 7º d.u.; PIS/COFINS no 11º d.u.</t>
         </is>
       </c>
       <c r="D24" s="356"/>
@@ -13809,12 +13809,12 @@
       <c r="H25" s="358"/>
       <c r="I25" s="358"/>
       <c r="J25" s="358"/>
-      <c r="K25" s="358"/>
-      <c r="L25" s="359" t="inlineStr">
+      <c r="K25" s="359" t="inlineStr">
         <is>
           <t xml:space="preserve">◆</t>
         </is>
       </c>
+      <c r="L25" s="340"/>
       <c r="M25" s="340"/>
       <c r="N25" s="340"/>
       <c r="O25" s="340"/>
@@ -13927,14 +13927,14 @@
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → correções do time Comber (1º ao 2º d.u.) → apurações, contabilidade e financeiro (3º d.u.) → folha (4º d.u.) → impostos (8º d.u.) → PIS/COFINS (11º d.u.) → balancete fechado (13º d.u.).</t>
+          <t xml:space="preserve">Ordem do fluxo: áreas operacionais (último dia) → trava e validação fiscal (1º d.u.) → correções do time Comber (1º ao 2º d.u.) → apurações, contabilidade e financeiro (3º d.u.) → folha (4º d.u.) → impostos (7º d.u.) → PIS/COFINS (11º d.u.) → balancete fechado (13º d.u.).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impostos: entrega 5 dias úteis após o início das apurações (3º d.u. + 5 = 8º d.u.). PIS/COFINS finalizado no 11º d.u.</t>
+          <t xml:space="preserve">Impostos (exceto PIS/COFINS) entregues no 7º d.u.; PIS/COFINS finalizado no 11º d.u.</t>
         </is>
       </c>
     </row>
